--- a/doc/新标日初级上册动词表.xlsx
+++ b/doc/新标日初级上册动词表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动词表" sheetId="1" r:id="R0a48088c57cc43c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="R2a66069ea20d4445"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动词表" sheetId="1" r:id="R8889f620ad3e47ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="Rd188cf04b5df4041"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1551,426 +1551,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">他；第17课已出现</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">触る</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">さわる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">碰、触摸、触</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">触ります</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">触って</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">脱ぐ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ぬぐ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">脱</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">脱ぎます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">脱いで</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">他；ぐ→いで</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">転ぶ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ころぶ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">摔、摔倒、跌倒</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">転びます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">転んで</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">渇く</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">かわく</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">渴</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">渇きます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">渇いて</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">治る</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">なおる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">痊愈、医好</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">治ります</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">治って</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">滑る</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">すべる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">滑、滑行</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">滑ります</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">滑って</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">呼ぶ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">よぶ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">呼喊、叫</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">呼びます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">呼んで</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">返す</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">かえす</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">归还</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">返します</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">返して</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">手伝う</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">てつだう</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">帮忙、帮助</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">手伝います</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">手伝って</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">運ぶ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">はこぶ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">搬运</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">運びます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">運んで</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">落とす</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">おとす</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">丢、丢失；弄掉</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">落とします</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">落として</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">置く</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">おく</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">放置</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">置きます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">置いて</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">払う</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">はらう</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">支付</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">払います</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">払って</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">立つ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">たつ</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">站、立</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">立ちます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">立って</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">忘れる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">わすれる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">忘记</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">忘れます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">忘れて</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">慌てる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">あわてる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">慌张、惊慌、着急</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">慌てます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">慌てて</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">捨てる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">すてる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">扔、扔掉</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">捨てます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">捨てて</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">残業する</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ざんぎょうする</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">加班</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">残業します</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">残業して</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">心配する</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">しんぱいする</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">担心、挂念</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">心配します</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">心配して</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">浴びる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">あびる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">淋、浇、沐浴</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">浴びます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">浴びて</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">集める</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">あつめる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">收集</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">集めます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">集めて</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">登る</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">のぼる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">登、上</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">登ります</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">登って</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">弾く</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">ひく</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">弹（琴等）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">弾きます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">弾いて</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">洗濯する</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">せんたくする</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">洗涤、洗衣服</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">洗濯します</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">洗濯して</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">予約する</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">よやくする</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">预约</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">予約します</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">予約して</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">着る</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">穿（上衣）</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">着ます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">着て</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">調べる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">しらべる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">调查、查（看）、弄清</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">調べます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">調べて</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">考える</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">かんがえる</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">考虑、思考</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">考えます</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">考えて</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">《新版中日交流标准日本语 初级 上册》第1—24课 动词一览表</x:t>
@@ -6001,815 +5581,815 @@
       </x:c>
     </x:row>
     <x:row r="108" ht="17">
-      <x:c r="A108" s="6">
+      <x:c r="A108" s="6" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B108" s="6" t="str">
+        <x:v>似合う</x:v>
+      </x:c>
+      <x:c r="C108" s="6" t="str">
+        <x:v>にあう</x:v>
+      </x:c>
+      <x:c r="D108" s="7" t="str">
+        <x:v>适合、相称</x:v>
+      </x:c>
+      <x:c r="E108" s="6" t="str">
+        <x:v>[2]</x:v>
+      </x:c>
+      <x:c r="F108" s="6" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G108" s="6" t="str">
+        <x:v>似合います</x:v>
+      </x:c>
+      <x:c r="H108" s="6" t="str">
+        <x:v>似合って</x:v>
+      </x:c>
+      <x:c r="I108" s="7" t="str">
+        <x:v>自</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="17">
+      <x:c r="A109" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B108" s="6" t="s">
-        <x:v>514</x:v>
-      </x:c>
-      <x:c r="C108" s="6" t="s">
-        <x:v>515</x:v>
-      </x:c>
-      <x:c r="D108" s="7" t="s">
-        <x:v>516</x:v>
-      </x:c>
-      <x:c r="E108" s="6" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F108" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G108" s="6" t="s">
-        <x:v>517</x:v>
-      </x:c>
-      <x:c r="H108" s="6" t="s">
-        <x:v>518</x:v>
-      </x:c>
-      <x:c r="I108" s="7" t="s">
-        <x:v>131</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" ht="17">
-      <x:c r="A109" s="8">
+      <x:c r="B109" s="8" t="str">
+        <x:v>触る</x:v>
+      </x:c>
+      <x:c r="C109" s="8" t="str">
+        <x:v>さわる</x:v>
+      </x:c>
+      <x:c r="D109" s="9" t="str">
+        <x:v>碰、触摸、触</x:v>
+      </x:c>
+      <x:c r="E109" s="8" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F109" s="8" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G109" s="8" t="str">
+        <x:v>触ります</x:v>
+      </x:c>
+      <x:c r="H109" s="8" t="str">
+        <x:v>触って</x:v>
+      </x:c>
+      <x:c r="I109" s="9" t="str">
+        <x:v>自/他视搭配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="17">
+      <x:c r="A110" s="6" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B109" s="8" t="s">
-        <x:v>519</x:v>
-      </x:c>
-      <x:c r="C109" s="8" t="s">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="D109" s="9" t="s">
-        <x:v>521</x:v>
-      </x:c>
-      <x:c r="E109" s="8" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F109" s="8" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G109" s="8" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="H109" s="8" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="I109" s="9" t="s">
-        <x:v>524</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="17">
-      <x:c r="A110" s="6">
+      <x:c r="B110" s="6" t="str">
+        <x:v>脱ぐ</x:v>
+      </x:c>
+      <x:c r="C110" s="6" t="str">
+        <x:v>ぬぐ</x:v>
+      </x:c>
+      <x:c r="D110" s="7" t="str">
+        <x:v>脱</x:v>
+      </x:c>
+      <x:c r="E110" s="6" t="str">
+        <x:v>[1]</x:v>
+      </x:c>
+      <x:c r="F110" s="6" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G110" s="6" t="str">
+        <x:v>脱ぎます</x:v>
+      </x:c>
+      <x:c r="H110" s="6" t="str">
+        <x:v>脱いで</x:v>
+      </x:c>
+      <x:c r="I110" s="7" t="str">
+        <x:v>他；ぐ→いで</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="17">
+      <x:c r="A111" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B110" s="6" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="C110" s="6" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="D110" s="7" t="s">
-        <x:v>527</x:v>
-      </x:c>
-      <x:c r="E110" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F110" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G110" s="6" t="s">
-        <x:v>528</x:v>
-      </x:c>
-      <x:c r="H110" s="6" t="s">
-        <x:v>529</x:v>
-      </x:c>
-      <x:c r="I110" s="7" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="17">
-      <x:c r="A111" s="8">
+      <x:c r="B111" s="8" t="str">
+        <x:v>転ぶ</x:v>
+      </x:c>
+      <x:c r="C111" s="8" t="str">
+        <x:v>ころぶ</x:v>
+      </x:c>
+      <x:c r="D111" s="9" t="str">
+        <x:v>摔、摔倒、跌倒</x:v>
+      </x:c>
+      <x:c r="E111" s="8" t="str">
+        <x:v>[2]</x:v>
+      </x:c>
+      <x:c r="F111" s="8" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G111" s="8" t="str">
+        <x:v>転びます</x:v>
+      </x:c>
+      <x:c r="H111" s="8" t="str">
+        <x:v>転んで</x:v>
+      </x:c>
+      <x:c r="I111" s="9" t="str">
+        <x:v>自</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="17">
+      <x:c r="A112" s="6" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B111" s="8" t="s">
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="C111" s="8" t="s">
-        <x:v>531</x:v>
-      </x:c>
-      <x:c r="D111" s="9" t="s">
-        <x:v>532</x:v>
-      </x:c>
-      <x:c r="E111" s="8" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F111" s="8" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G111" s="8" t="s">
-        <x:v>533</x:v>
-      </x:c>
-      <x:c r="H111" s="8" t="s">
-        <x:v>534</x:v>
-      </x:c>
-      <x:c r="I111" s="9" t="s">
-        <x:v>271</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" ht="17">
-      <x:c r="A112" s="6">
+      <x:c r="B112" s="6" t="str">
+        <x:v>渇く</x:v>
+      </x:c>
+      <x:c r="C112" s="6" t="str">
+        <x:v>かわく</x:v>
+      </x:c>
+      <x:c r="D112" s="7" t="str">
+        <x:v>渴</x:v>
+      </x:c>
+      <x:c r="E112" s="6" t="str">
+        <x:v>[2]</x:v>
+      </x:c>
+      <x:c r="F112" s="6" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G112" s="6" t="str">
+        <x:v>渇きます</x:v>
+      </x:c>
+      <x:c r="H112" s="6" t="str">
+        <x:v>渇いて</x:v>
+      </x:c>
+      <x:c r="I112" s="7" t="str">
+        <x:v>自；い音便</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="17">
+      <x:c r="A113" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B112" s="6" t="s">
-        <x:v>535</x:v>
-      </x:c>
-      <x:c r="C112" s="6" t="s">
-        <x:v>536</x:v>
-      </x:c>
-      <x:c r="D112" s="7" t="s">
-        <x:v>537</x:v>
-      </x:c>
-      <x:c r="E112" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F112" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G112" s="6" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="H112" s="6" t="s">
-        <x:v>539</x:v>
-      </x:c>
-      <x:c r="I112" s="7" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="17">
-      <x:c r="A113" s="8">
+      <x:c r="B113" s="8" t="str">
+        <x:v>治る</x:v>
+      </x:c>
+      <x:c r="C113" s="8" t="str">
+        <x:v>なおる</x:v>
+      </x:c>
+      <x:c r="D113" s="9" t="str">
+        <x:v>痊愈、医好</x:v>
+      </x:c>
+      <x:c r="E113" s="8" t="str">
+        <x:v>[2]</x:v>
+      </x:c>
+      <x:c r="F113" s="8" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G113" s="8" t="str">
+        <x:v>治ります</x:v>
+      </x:c>
+      <x:c r="H113" s="8" t="str">
+        <x:v>治って</x:v>
+      </x:c>
+      <x:c r="I113" s="9" t="str">
+        <x:v>自</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="17">
+      <x:c r="A114" s="6" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B113" s="8" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="C113" s="8" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="D113" s="9" t="s">
-        <x:v>542</x:v>
-      </x:c>
-      <x:c r="E113" s="8" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F113" s="8" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G113" s="8" t="s">
-        <x:v>543</x:v>
-      </x:c>
-      <x:c r="H113" s="8" t="s">
-        <x:v>544</x:v>
-      </x:c>
-      <x:c r="I113" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" ht="17">
-      <x:c r="A114" s="6">
+      <x:c r="B114" s="6" t="str">
+        <x:v>滑る</x:v>
+      </x:c>
+      <x:c r="C114" s="6" t="str">
+        <x:v>すべる</x:v>
+      </x:c>
+      <x:c r="D114" s="7" t="str">
+        <x:v>滑、滑行</x:v>
+      </x:c>
+      <x:c r="E114" s="6" t="str">
+        <x:v>[2]</x:v>
+      </x:c>
+      <x:c r="F114" s="6" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G114" s="6" t="str">
+        <x:v>滑ります</x:v>
+      </x:c>
+      <x:c r="H114" s="6" t="str">
+        <x:v>滑って</x:v>
+      </x:c>
+      <x:c r="I114" s="7" t="str">
+        <x:v>自</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="17">
+      <x:c r="A115" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B114" s="6" t="s">
-        <x:v>545</x:v>
-      </x:c>
-      <x:c r="C114" s="6" t="s">
-        <x:v>546</x:v>
-      </x:c>
-      <x:c r="D114" s="7" t="s">
-        <x:v>547</x:v>
-      </x:c>
-      <x:c r="E114" s="6" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F114" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G114" s="6" t="s">
-        <x:v>548</x:v>
-      </x:c>
-      <x:c r="H114" s="6" t="s">
-        <x:v>549</x:v>
-      </x:c>
-      <x:c r="I114" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" ht="17">
-      <x:c r="A115" s="8">
+      <x:c r="B115" s="8" t="str">
+        <x:v>呼ぶ</x:v>
+      </x:c>
+      <x:c r="C115" s="8" t="str">
+        <x:v>よぶ</x:v>
+      </x:c>
+      <x:c r="D115" s="9" t="str">
+        <x:v>呼喊、叫</x:v>
+      </x:c>
+      <x:c r="E115" s="8" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F115" s="8" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G115" s="8" t="str">
+        <x:v>呼びます</x:v>
+      </x:c>
+      <x:c r="H115" s="8" t="str">
+        <x:v>呼んで</x:v>
+      </x:c>
+      <x:c r="I115" s="9" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="17">
+      <x:c r="A116" s="6" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B115" s="8" t="s">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="C115" s="8" t="s">
-        <x:v>551</x:v>
-      </x:c>
-      <x:c r="D115" s="9" t="s">
-        <x:v>552</x:v>
-      </x:c>
-      <x:c r="E115" s="8" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F115" s="8" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G115" s="8" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="H115" s="8" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="I115" s="9" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" ht="17">
-      <x:c r="A116" s="6">
+      <x:c r="B116" s="6" t="str">
+        <x:v>返す</x:v>
+      </x:c>
+      <x:c r="C116" s="6" t="str">
+        <x:v>かえす</x:v>
+      </x:c>
+      <x:c r="D116" s="7" t="str">
+        <x:v>归还</x:v>
+      </x:c>
+      <x:c r="E116" s="6" t="str">
+        <x:v>[1]</x:v>
+      </x:c>
+      <x:c r="F116" s="6" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G116" s="6" t="str">
+        <x:v>返します</x:v>
+      </x:c>
+      <x:c r="H116" s="6" t="str">
+        <x:v>返して</x:v>
+      </x:c>
+      <x:c r="I116" s="7" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="17">
+      <x:c r="A117" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B116" s="6" t="s">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="C116" s="6" t="s">
-        <x:v>556</x:v>
-      </x:c>
-      <x:c r="D116" s="7" t="s">
-        <x:v>557</x:v>
-      </x:c>
-      <x:c r="E116" s="6" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="F116" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G116" s="6" t="s">
-        <x:v>558</x:v>
-      </x:c>
-      <x:c r="H116" s="6" t="s">
-        <x:v>559</x:v>
-      </x:c>
-      <x:c r="I116" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" ht="17">
-      <x:c r="A117" s="8">
+      <x:c r="B117" s="8" t="str">
+        <x:v>手伝う</x:v>
+      </x:c>
+      <x:c r="C117" s="8" t="str">
+        <x:v>てつだう</x:v>
+      </x:c>
+      <x:c r="D117" s="9" t="str">
+        <x:v>帮忙、帮助</x:v>
+      </x:c>
+      <x:c r="E117" s="8" t="str">
+        <x:v>[3]</x:v>
+      </x:c>
+      <x:c r="F117" s="8" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G117" s="8" t="str">
+        <x:v>手伝います</x:v>
+      </x:c>
+      <x:c r="H117" s="8" t="str">
+        <x:v>手伝って</x:v>
+      </x:c>
+      <x:c r="I117" s="9" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="17">
+      <x:c r="A118" s="6" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B117" s="8" t="s">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="C117" s="8" t="s">
-        <x:v>561</x:v>
-      </x:c>
-      <x:c r="D117" s="9" t="s">
-        <x:v>562</x:v>
-      </x:c>
-      <x:c r="E117" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F117" s="8" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G117" s="8" t="s">
-        <x:v>563</x:v>
-      </x:c>
-      <x:c r="H117" s="8" t="s">
-        <x:v>564</x:v>
-      </x:c>
-      <x:c r="I117" s="9" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" ht="17">
-      <x:c r="A118" s="6">
+      <x:c r="B118" s="6" t="str">
+        <x:v>運ぶ</x:v>
+      </x:c>
+      <x:c r="C118" s="6" t="str">
+        <x:v>はこぶ</x:v>
+      </x:c>
+      <x:c r="D118" s="7" t="str">
+        <x:v>搬运</x:v>
+      </x:c>
+      <x:c r="E118" s="6" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F118" s="6" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G118" s="6" t="str">
+        <x:v>運びます</x:v>
+      </x:c>
+      <x:c r="H118" s="6" t="str">
+        <x:v>運んで</x:v>
+      </x:c>
+      <x:c r="I118" s="7" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="17">
+      <x:c r="A119" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B118" s="6" t="s">
-        <x:v>565</x:v>
-      </x:c>
-      <x:c r="C118" s="6" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="D118" s="7" t="s">
-        <x:v>567</x:v>
-      </x:c>
-      <x:c r="E118" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F118" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G118" s="6" t="s">
-        <x:v>568</x:v>
-      </x:c>
-      <x:c r="H118" s="6" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="I118" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" ht="17">
-      <x:c r="A119" s="8">
+      <x:c r="B119" s="8" t="str">
+        <x:v>落とす</x:v>
+      </x:c>
+      <x:c r="C119" s="8" t="str">
+        <x:v>おとす</x:v>
+      </x:c>
+      <x:c r="D119" s="9" t="str">
+        <x:v>丢、丢失；弄掉</x:v>
+      </x:c>
+      <x:c r="E119" s="8" t="str">
+        <x:v>[2]</x:v>
+      </x:c>
+      <x:c r="F119" s="8" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G119" s="8" t="str">
+        <x:v>落とします</x:v>
+      </x:c>
+      <x:c r="H119" s="8" t="str">
+        <x:v>落として</x:v>
+      </x:c>
+      <x:c r="I119" s="9" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="17">
+      <x:c r="A120" s="6" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B119" s="8" t="s">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="C119" s="8" t="s">
-        <x:v>571</x:v>
-      </x:c>
-      <x:c r="D119" s="9" t="s">
-        <x:v>572</x:v>
-      </x:c>
-      <x:c r="E119" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F119" s="8" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G119" s="8" t="s">
-        <x:v>573</x:v>
-      </x:c>
-      <x:c r="H119" s="8" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="I119" s="9" t="s">
-        <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" ht="17">
-      <x:c r="A120" s="6">
+      <x:c r="B120" s="6" t="str">
+        <x:v>置く</x:v>
+      </x:c>
+      <x:c r="C120" s="6" t="str">
+        <x:v>おく</x:v>
+      </x:c>
+      <x:c r="D120" s="7" t="str">
+        <x:v>放置</x:v>
+      </x:c>
+      <x:c r="E120" s="6" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F120" s="6" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G120" s="6" t="str">
+        <x:v>置きます</x:v>
+      </x:c>
+      <x:c r="H120" s="6" t="str">
+        <x:v>置いて</x:v>
+      </x:c>
+      <x:c r="I120" s="7" t="str">
+        <x:v>他；い音便</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="17">
+      <x:c r="A121" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B120" s="6" t="s">
-        <x:v>575</x:v>
-      </x:c>
-      <x:c r="C120" s="6" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="D120" s="7" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="E120" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F120" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G120" s="6" t="s">
-        <x:v>578</x:v>
-      </x:c>
-      <x:c r="H120" s="6" t="s">
-        <x:v>579</x:v>
-      </x:c>
-      <x:c r="I120" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" ht="17">
-      <x:c r="A121" s="8">
+      <x:c r="B121" s="8" t="str">
+        <x:v>払う</x:v>
+      </x:c>
+      <x:c r="C121" s="8" t="str">
+        <x:v>はらう</x:v>
+      </x:c>
+      <x:c r="D121" s="9" t="str">
+        <x:v>支付</x:v>
+      </x:c>
+      <x:c r="E121" s="8" t="str">
+        <x:v>[2]</x:v>
+      </x:c>
+      <x:c r="F121" s="8" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G121" s="8" t="str">
+        <x:v>払います</x:v>
+      </x:c>
+      <x:c r="H121" s="8" t="str">
+        <x:v>払って</x:v>
+      </x:c>
+      <x:c r="I121" s="9" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="17">
+      <x:c r="A122" s="6" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B121" s="8" t="s">
-        <x:v>580</x:v>
-      </x:c>
-      <x:c r="C121" s="8" t="s">
-        <x:v>581</x:v>
-      </x:c>
-      <x:c r="D121" s="9" t="s">
-        <x:v>582</x:v>
-      </x:c>
-      <x:c r="E121" s="8" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F121" s="8" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G121" s="8" t="s">
-        <x:v>583</x:v>
-      </x:c>
-      <x:c r="H121" s="8" t="s">
-        <x:v>584</x:v>
-      </x:c>
-      <x:c r="I121" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" ht="17">
-      <x:c r="A122" s="6">
+      <x:c r="B122" s="6" t="str">
+        <x:v>立つ</x:v>
+      </x:c>
+      <x:c r="C122" s="6" t="str">
+        <x:v>たつ</x:v>
+      </x:c>
+      <x:c r="D122" s="7" t="str">
+        <x:v>站、立</x:v>
+      </x:c>
+      <x:c r="E122" s="6" t="str">
+        <x:v>[1]</x:v>
+      </x:c>
+      <x:c r="F122" s="6" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G122" s="6" t="str">
+        <x:v>立ちます</x:v>
+      </x:c>
+      <x:c r="H122" s="6" t="str">
+        <x:v>立って</x:v>
+      </x:c>
+      <x:c r="I122" s="7" t="str">
+        <x:v>自</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="17">
+      <x:c r="A123" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B122" s="6" t="s">
-        <x:v>585</x:v>
-      </x:c>
-      <x:c r="C122" s="6" t="s">
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="D122" s="7" t="s">
-        <x:v>587</x:v>
-      </x:c>
-      <x:c r="E122" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F122" s="6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G122" s="6" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="H122" s="6" t="s">
-        <x:v>589</x:v>
-      </x:c>
-      <x:c r="I122" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" ht="17">
-      <x:c r="A123" s="8">
+      <x:c r="B123" s="8" t="str">
+        <x:v>忘れる</x:v>
+      </x:c>
+      <x:c r="C123" s="8" t="str">
+        <x:v>わすれる</x:v>
+      </x:c>
+      <x:c r="D123" s="9" t="str">
+        <x:v>忘记</x:v>
+      </x:c>
+      <x:c r="E123" s="8" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F123" s="8" t="str">
+        <x:v>二类（一段）</x:v>
+      </x:c>
+      <x:c r="G123" s="8" t="str">
+        <x:v>忘れます</x:v>
+      </x:c>
+      <x:c r="H123" s="8" t="str">
+        <x:v>忘れて</x:v>
+      </x:c>
+      <x:c r="I123" s="9" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="17">
+      <x:c r="A124" s="6" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B123" s="8" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="C123" s="8" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="D123" s="9" t="s">
-        <x:v>592</x:v>
-      </x:c>
-      <x:c r="E123" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F123" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G123" s="8" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="H123" s="8" t="s">
-        <x:v>594</x:v>
-      </x:c>
-      <x:c r="I123" s="9" t="s">
-        <x:v>131</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" ht="17">
-      <x:c r="A124" s="6">
+      <x:c r="B124" s="6" t="str">
+        <x:v>慌てる</x:v>
+      </x:c>
+      <x:c r="C124" s="6" t="str">
+        <x:v>あわてる</x:v>
+      </x:c>
+      <x:c r="D124" s="7" t="str">
+        <x:v>慌张、惊慌、着急</x:v>
+      </x:c>
+      <x:c r="E124" s="6" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F124" s="6" t="str">
+        <x:v>二类（一段）</x:v>
+      </x:c>
+      <x:c r="G124" s="6" t="str">
+        <x:v>慌てます</x:v>
+      </x:c>
+      <x:c r="H124" s="6" t="str">
+        <x:v>慌てて</x:v>
+      </x:c>
+      <x:c r="I124" s="7" t="str">
+        <x:v>自/他视搭配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="17">
+      <x:c r="A125" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B124" s="6" t="s">
-        <x:v>595</x:v>
-      </x:c>
-      <x:c r="C124" s="6" t="s">
-        <x:v>596</x:v>
-      </x:c>
-      <x:c r="D124" s="7" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="E124" s="6" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F124" s="6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G124" s="6" t="s">
-        <x:v>598</x:v>
-      </x:c>
-      <x:c r="H124" s="6" t="s">
-        <x:v>599</x:v>
-      </x:c>
-      <x:c r="I124" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" ht="17">
-      <x:c r="A125" s="8">
+      <x:c r="B125" s="8" t="str">
+        <x:v>捨てる</x:v>
+      </x:c>
+      <x:c r="C125" s="8" t="str">
+        <x:v>すてる</x:v>
+      </x:c>
+      <x:c r="D125" s="9" t="str">
+        <x:v>扔、扔掉</x:v>
+      </x:c>
+      <x:c r="E125" s="8" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F125" s="8" t="str">
+        <x:v>二类（一段）</x:v>
+      </x:c>
+      <x:c r="G125" s="8" t="str">
+        <x:v>捨てます</x:v>
+      </x:c>
+      <x:c r="H125" s="8" t="str">
+        <x:v>捨てて</x:v>
+      </x:c>
+      <x:c r="I125" s="9" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="17">
+      <x:c r="A126" s="6" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B125" s="8" t="s">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="C125" s="8" t="s">
-        <x:v>601</x:v>
-      </x:c>
-      <x:c r="D125" s="9" t="s">
-        <x:v>602</x:v>
-      </x:c>
-      <x:c r="E125" s="8" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F125" s="8" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G125" s="8" t="s">
-        <x:v>603</x:v>
-      </x:c>
-      <x:c r="H125" s="8" t="s">
-        <x:v>604</x:v>
-      </x:c>
-      <x:c r="I125" s="9" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" ht="17">
-      <x:c r="A126" s="6">
+      <x:c r="B126" s="6" t="str">
+        <x:v>残業する</x:v>
+      </x:c>
+      <x:c r="C126" s="6" t="str">
+        <x:v>ざんぎょうする</x:v>
+      </x:c>
+      <x:c r="D126" s="7" t="str">
+        <x:v>加班</x:v>
+      </x:c>
+      <x:c r="E126" s="6" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F126" s="6" t="str">
+        <x:v>三类（サ变）</x:v>
+      </x:c>
+      <x:c r="G126" s="6" t="str">
+        <x:v>残業します</x:v>
+      </x:c>
+      <x:c r="H126" s="6" t="str">
+        <x:v>残業して</x:v>
+      </x:c>
+      <x:c r="I126" s="7" t="str">
+        <x:v>自</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="17">
+      <x:c r="A127" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B126" s="6" t="s">
-        <x:v>605</x:v>
-      </x:c>
-      <x:c r="C126" s="6" t="s">
-        <x:v>606</x:v>
-      </x:c>
-      <x:c r="D126" s="7" t="s">
-        <x:v>607</x:v>
-      </x:c>
-      <x:c r="E126" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F126" s="6" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G126" s="6" t="s">
-        <x:v>608</x:v>
-      </x:c>
-      <x:c r="H126" s="6" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="I126" s="7" t="s">
-        <x:v>131</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" ht="17">
-      <x:c r="A127" s="8">
+      <x:c r="B127" s="8" t="str">
+        <x:v>心配する</x:v>
+      </x:c>
+      <x:c r="C127" s="8" t="str">
+        <x:v>しんぱいする</x:v>
+      </x:c>
+      <x:c r="D127" s="9" t="str">
+        <x:v>担心、挂念</x:v>
+      </x:c>
+      <x:c r="E127" s="8" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F127" s="8" t="str">
+        <x:v>三类（サ变）</x:v>
+      </x:c>
+      <x:c r="G127" s="8" t="str">
+        <x:v>心配します</x:v>
+      </x:c>
+      <x:c r="H127" s="8" t="str">
+        <x:v>心配して</x:v>
+      </x:c>
+      <x:c r="I127" s="9" t="str">
+        <x:v>自/他视搭配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="17">
+      <x:c r="A128" s="6" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B127" s="8" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="C127" s="8" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="D127" s="9" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="E127" s="8" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F127" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G127" s="8" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="H127" s="8" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="I127" s="9" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" ht="17">
-      <x:c r="A128" s="6">
+      <x:c r="B128" s="6" t="str">
+        <x:v>浴びる</x:v>
+      </x:c>
+      <x:c r="C128" s="6" t="str">
+        <x:v>あびる</x:v>
+      </x:c>
+      <x:c r="D128" s="7" t="str">
+        <x:v>淋、浇、沐浴</x:v>
+      </x:c>
+      <x:c r="E128" s="6" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F128" s="6" t="str">
+        <x:v>二类（一段）</x:v>
+      </x:c>
+      <x:c r="G128" s="6" t="str">
+        <x:v>浴びます</x:v>
+      </x:c>
+      <x:c r="H128" s="6" t="str">
+        <x:v>浴びて</x:v>
+      </x:c>
+      <x:c r="I128" s="7" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="17">
+      <x:c r="A129" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B128" s="6" t="s">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c r="C128" s="6" t="s">
-        <x:v>616</x:v>
-      </x:c>
-      <x:c r="D128" s="7" t="s">
-        <x:v>617</x:v>
-      </x:c>
-      <x:c r="E128" s="6" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="F128" s="6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G128" s="6" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="H128" s="6" t="s">
-        <x:v>619</x:v>
-      </x:c>
-      <x:c r="I128" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" ht="17">
-      <x:c r="A129" s="8">
+      <x:c r="B129" s="8" t="str">
+        <x:v>集める</x:v>
+      </x:c>
+      <x:c r="C129" s="8" t="str">
+        <x:v>あつめる</x:v>
+      </x:c>
+      <x:c r="D129" s="9" t="str">
+        <x:v>收集</x:v>
+      </x:c>
+      <x:c r="E129" s="8" t="str">
+        <x:v>[3]</x:v>
+      </x:c>
+      <x:c r="F129" s="8" t="str">
+        <x:v>二类（一段）</x:v>
+      </x:c>
+      <x:c r="G129" s="8" t="str">
+        <x:v>集めます</x:v>
+      </x:c>
+      <x:c r="H129" s="8" t="str">
+        <x:v>集めて</x:v>
+      </x:c>
+      <x:c r="I129" s="9" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="17">
+      <x:c r="A130" s="6" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B129" s="8" t="s">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c r="C129" s="8" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="D129" s="9" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="E129" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F129" s="8" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G129" s="8" t="s">
-        <x:v>623</x:v>
-      </x:c>
-      <x:c r="H129" s="8" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="I129" s="9" t="s">
-        <x:v>131</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" ht="17">
-      <x:c r="A130" s="6">
+      <x:c r="B130" s="6" t="str">
+        <x:v>登る</x:v>
+      </x:c>
+      <x:c r="C130" s="6" t="str">
+        <x:v>のぼる</x:v>
+      </x:c>
+      <x:c r="D130" s="7" t="str">
+        <x:v>登、上</x:v>
+      </x:c>
+      <x:c r="E130" s="6" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F130" s="6" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G130" s="6" t="str">
+        <x:v>登ります</x:v>
+      </x:c>
+      <x:c r="H130" s="6" t="str">
+        <x:v>登って</x:v>
+      </x:c>
+      <x:c r="I130" s="7" t="str">
+        <x:v>自/他视搭配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="17">
+      <x:c r="A131" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="B130" s="6" t="s">
-        <x:v>625</x:v>
-      </x:c>
-      <x:c r="C130" s="6" t="s">
-        <x:v>626</x:v>
-      </x:c>
-      <x:c r="D130" s="7" t="s">
-        <x:v>627</x:v>
-      </x:c>
-      <x:c r="E130" s="6" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F130" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G130" s="6" t="s">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="H130" s="6" t="s">
-        <x:v>629</x:v>
-      </x:c>
-      <x:c r="I130" s="7" t="s">
-        <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" ht="17">
-      <x:c r="A131" s="8">
+      <x:c r="B131" s="8" t="str">
+        <x:v>弾く</x:v>
+      </x:c>
+      <x:c r="C131" s="8" t="str">
+        <x:v>ひく</x:v>
+      </x:c>
+      <x:c r="D131" s="9" t="str">
+        <x:v>弹（琴等）</x:v>
+      </x:c>
+      <x:c r="E131" s="8" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F131" s="8" t="str">
+        <x:v>一类（五段）</x:v>
+      </x:c>
+      <x:c r="G131" s="8" t="str">
+        <x:v>弾きます</x:v>
+      </x:c>
+      <x:c r="H131" s="8" t="str">
+        <x:v>弾いて</x:v>
+      </x:c>
+      <x:c r="I131" s="9" t="str">
+        <x:v>他；い音便</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="17">
+      <x:c r="A132" s="6" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B131" s="8" t="s">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="C131" s="8" t="s">
-        <x:v>631</x:v>
-      </x:c>
-      <x:c r="D131" s="9" t="s">
-        <x:v>632</x:v>
-      </x:c>
-      <x:c r="E131" s="8" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F131" s="8" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G131" s="8" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="H131" s="8" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="I131" s="9" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" ht="17">
-      <x:c r="A132" s="6">
+      <x:c r="B132" s="6" t="str">
+        <x:v>洗濯する</x:v>
+      </x:c>
+      <x:c r="C132" s="6" t="str">
+        <x:v>せんたくする</x:v>
+      </x:c>
+      <x:c r="D132" s="7" t="str">
+        <x:v>洗涤、洗衣服</x:v>
+      </x:c>
+      <x:c r="E132" s="6" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F132" s="6" t="str">
+        <x:v>三类（サ变）</x:v>
+      </x:c>
+      <x:c r="G132" s="6" t="str">
+        <x:v>洗濯します</x:v>
+      </x:c>
+      <x:c r="H132" s="6" t="str">
+        <x:v>洗濯して</x:v>
+      </x:c>
+      <x:c r="I132" s="7" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="17">
+      <x:c r="A133" s="8" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B132" s="6" t="s">
-        <x:v>635</x:v>
-      </x:c>
-      <x:c r="C132" s="6" t="s">
-        <x:v>636</x:v>
-      </x:c>
-      <x:c r="D132" s="7" t="s">
-        <x:v>637</x:v>
-      </x:c>
-      <x:c r="E132" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F132" s="6" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G132" s="6" t="s">
-        <x:v>638</x:v>
-      </x:c>
-      <x:c r="H132" s="6" t="s">
-        <x:v>639</x:v>
-      </x:c>
-      <x:c r="I132" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" ht="17">
-      <x:c r="A133" s="8">
+      <x:c r="B133" s="8" t="str">
+        <x:v>予約する</x:v>
+      </x:c>
+      <x:c r="C133" s="8" t="str">
+        <x:v>よやくする</x:v>
+      </x:c>
+      <x:c r="D133" s="9" t="str">
+        <x:v>预约</x:v>
+      </x:c>
+      <x:c r="E133" s="8" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F133" s="8" t="str">
+        <x:v>三类（サ变）</x:v>
+      </x:c>
+      <x:c r="G133" s="8" t="str">
+        <x:v>予約します</x:v>
+      </x:c>
+      <x:c r="H133" s="8" t="str">
+        <x:v>予約して</x:v>
+      </x:c>
+      <x:c r="I133" s="9" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="17">
+      <x:c r="A134" s="6" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B133" s="8" t="s">
-        <x:v>640</x:v>
-      </x:c>
-      <x:c r="C133" s="8" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="D133" s="9" t="s">
-        <x:v>641</x:v>
-      </x:c>
-      <x:c r="E133" s="8" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="F133" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G133" s="8" t="s">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="H133" s="8" t="s">
-        <x:v>643</x:v>
-      </x:c>
-      <x:c r="I133" s="9" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" ht="17">
-      <x:c r="A134" s="6">
+      <x:c r="B134" s="6" t="str">
+        <x:v>着る</x:v>
+      </x:c>
+      <x:c r="C134" s="6" t="str">
+        <x:v>きる</x:v>
+      </x:c>
+      <x:c r="D134" s="7" t="str">
+        <x:v>穿（上衣）</x:v>
+      </x:c>
+      <x:c r="E134" s="6" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F134" s="6" t="str">
+        <x:v>二类（一段）</x:v>
+      </x:c>
+      <x:c r="G134" s="6" t="str">
+        <x:v>着ます</x:v>
+      </x:c>
+      <x:c r="H134" s="6" t="str">
+        <x:v>着て</x:v>
+      </x:c>
+      <x:c r="I134" s="7" t="str">
+        <x:v>他</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="17">
+      <x:c r="A135" s="8" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B134" s="6" t="s">
-        <x:v>644</x:v>
-      </x:c>
-      <x:c r="C134" s="6" t="s">
-        <x:v>645</x:v>
-      </x:c>
-      <x:c r="D134" s="7" t="s">
-        <x:v>646</x:v>
-      </x:c>
-      <x:c r="E134" s="6" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="F134" s="6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G134" s="6" t="s">
-        <x:v>647</x:v>
-      </x:c>
-      <x:c r="H134" s="6" t="s">
-        <x:v>648</x:v>
-      </x:c>
-      <x:c r="I134" s="7" t="s">
-        <x:v>100</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" ht="17">
-      <x:c r="A135" s="8">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B135" s="8" t="s">
-        <x:v>649</x:v>
-      </x:c>
-      <x:c r="C135" s="8" t="s">
-        <x:v>650</x:v>
-      </x:c>
-      <x:c r="D135" s="9" t="s">
-        <x:v>651</x:v>
-      </x:c>
-      <x:c r="E135" s="8" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F135" s="8" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G135" s="8" t="s">
-        <x:v>652</x:v>
-      </x:c>
-      <x:c r="H135" s="8" t="s">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="I135" s="9" t="s">
-        <x:v>479</x:v>
+      <x:c r="B135" s="8" t="str">
+        <x:v>調べる</x:v>
+      </x:c>
+      <x:c r="C135" s="8" t="str">
+        <x:v>しらべる</x:v>
+      </x:c>
+      <x:c r="D135" s="9" t="str">
+        <x:v>调查、查（看）、弄清</x:v>
+      </x:c>
+      <x:c r="E135" s="8" t="str">
+        <x:v>[3]</x:v>
+      </x:c>
+      <x:c r="F135" s="8" t="str">
+        <x:v>二类（一段）</x:v>
+      </x:c>
+      <x:c r="G135" s="8" t="str">
+        <x:v>調べます</x:v>
+      </x:c>
+      <x:c r="H135" s="8" t="str">
+        <x:v>調べて</x:v>
+      </x:c>
+      <x:c r="I135" s="9" t="str">
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="34">
@@ -6817,57 +6397,57 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B136" s="6" t="str">
-        <x:v>遅れる</x:v>
+        <x:v>考える</x:v>
       </x:c>
       <x:c r="C136" s="6" t="str">
-        <x:v>おくれる</x:v>
+        <x:v>かんがえる</x:v>
       </x:c>
       <x:c r="D136" s="7" t="str">
-        <x:v>迟到、晚</x:v>
+        <x:v>考虑、思考</x:v>
       </x:c>
       <x:c r="E136" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F136" s="6" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G136" s="6" t="str">
-        <x:v>遅れます</x:v>
+        <x:v>考えます</x:v>
       </x:c>
       <x:c r="H136" s="6" t="str">
-        <x:v>遅れて</x:v>
+        <x:v>考えて</x:v>
       </x:c>
       <x:c r="I136" s="7" t="str">
-        <x:v>自</x:v>
+        <x:v>他/自视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="17">
       <x:c r="A137" s="8" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B137" s="8" t="str">
-        <x:v>見る</x:v>
+        <x:v>遅れる</x:v>
       </x:c>
       <x:c r="C137" s="8" t="str">
-        <x:v>みる</x:v>
+        <x:v>おくれる</x:v>
       </x:c>
       <x:c r="D137" s="9" t="str">
-        <x:v>看、观看</x:v>
+        <x:v>迟到、晚</x:v>
       </x:c>
       <x:c r="E137" s="8" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F137" s="8" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G137" s="8" t="str">
-        <x:v>見ます</x:v>
+        <x:v>遅れます</x:v>
       </x:c>
       <x:c r="H137" s="8" t="str">
-        <x:v>見て</x:v>
+        <x:v>遅れて</x:v>
       </x:c>
       <x:c r="I137" s="9" t="str">
-        <x:v>他；第7课已出现，语法例句复用</x:v>
+        <x:v>自</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="17">
@@ -6875,28 +6455,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B138" s="6" t="str">
-        <x:v>する</x:v>
+        <x:v>見る</x:v>
       </x:c>
       <x:c r="C138" s="6" t="str">
-        <x:v>する</x:v>
+        <x:v>みる</x:v>
       </x:c>
       <x:c r="D138" s="7" t="str">
-        <x:v>做、干</x:v>
+        <x:v>看、观看</x:v>
       </x:c>
       <x:c r="E138" s="6" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F138" s="6" t="str">
-        <x:v>三类（サ变）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G138" s="6" t="str">
-        <x:v>します</x:v>
+        <x:v>見ます</x:v>
       </x:c>
       <x:c r="H138" s="6" t="str">
-        <x:v>して</x:v>
+        <x:v>見て</x:v>
       </x:c>
       <x:c r="I138" s="7" t="str">
-        <x:v>第7课已出现</x:v>
+        <x:v>他；第7课已出现，语法例句复用</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="17">
@@ -6904,28 +6484,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B139" s="8" t="str">
-        <x:v>言う</x:v>
+        <x:v>する</x:v>
       </x:c>
       <x:c r="C139" s="8" t="str">
-        <x:v>いう</x:v>
+        <x:v>する</x:v>
       </x:c>
       <x:c r="D139" s="9" t="str">
-        <x:v>说、讲</x:v>
+        <x:v>做、干</x:v>
       </x:c>
       <x:c r="E139" s="8" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F139" s="8" t="str">
-        <x:v>一类（五段）</x:v>
+        <x:v>三类（サ变）</x:v>
       </x:c>
       <x:c r="G139" s="8" t="str">
-        <x:v>言います</x:v>
+        <x:v>します</x:v>
       </x:c>
       <x:c r="H139" s="8" t="str">
-        <x:v>言って</x:v>
+        <x:v>して</x:v>
       </x:c>
       <x:c r="I139" s="9" t="str">
-        <x:v>他</x:v>
+        <x:v>第7课已出现</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="17">
@@ -6933,13 +6513,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B140" s="6" t="str">
-        <x:v>帰る</x:v>
+        <x:v>言う</x:v>
       </x:c>
       <x:c r="C140" s="6" t="str">
-        <x:v>かえる</x:v>
+        <x:v>いう</x:v>
       </x:c>
       <x:c r="D140" s="7" t="str">
-        <x:v>回、回去</x:v>
+        <x:v>说、讲</x:v>
       </x:c>
       <x:c r="E140" s="6" t="str">
         <x:v>待核</x:v>
@@ -6948,42 +6528,42 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G140" s="6" t="str">
-        <x:v>帰ります</x:v>
+        <x:v>言います</x:v>
       </x:c>
       <x:c r="H140" s="6" t="str">
-        <x:v>帰って</x:v>
+        <x:v>言って</x:v>
       </x:c>
       <x:c r="I140" s="7" t="str">
-        <x:v>自；第6课已出现</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="17">
       <x:c r="A141" s="8" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B141" s="8" t="str">
-        <x:v>違う</x:v>
+        <x:v>帰る</x:v>
       </x:c>
       <x:c r="C141" s="8" t="str">
-        <x:v>ちがう</x:v>
+        <x:v>かえる</x:v>
       </x:c>
       <x:c r="D141" s="9" t="str">
-        <x:v>不同、不一样</x:v>
+        <x:v>回、回去</x:v>
       </x:c>
       <x:c r="E141" s="8" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F141" s="8" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G141" s="8" t="str">
-        <x:v>違います</x:v>
+        <x:v>帰ります</x:v>
       </x:c>
       <x:c r="H141" s="8" t="str">
-        <x:v>違って</x:v>
+        <x:v>帰って</x:v>
       </x:c>
       <x:c r="I141" s="9" t="str">
-        <x:v>自</x:v>
+        <x:v>自；第6课已出现</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="17">
@@ -6991,25 +6571,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B142" s="6" t="str">
-        <x:v>混む</x:v>
+        <x:v>違う</x:v>
       </x:c>
       <x:c r="C142" s="6" t="str">
-        <x:v>こむ</x:v>
+        <x:v>ちがう</x:v>
       </x:c>
       <x:c r="D142" s="7" t="str">
-        <x:v>拥挤、混杂</x:v>
+        <x:v>不同、不一样</x:v>
       </x:c>
       <x:c r="E142" s="6" t="str">
-        <x:v>[1]</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F142" s="6" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G142" s="6" t="str">
-        <x:v>混みます</x:v>
+        <x:v>違います</x:v>
       </x:c>
       <x:c r="H142" s="6" t="str">
-        <x:v>混んで</x:v>
+        <x:v>違って</x:v>
       </x:c>
       <x:c r="I142" s="7" t="str">
         <x:v>自</x:v>
@@ -7020,25 +6600,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B143" s="8" t="str">
-        <x:v>決まる</x:v>
+        <x:v>混む</x:v>
       </x:c>
       <x:c r="C143" s="8" t="str">
-        <x:v>きまる</x:v>
+        <x:v>こむ</x:v>
       </x:c>
       <x:c r="D143" s="9" t="str">
-        <x:v>定、决定</x:v>
+        <x:v>拥挤、混杂</x:v>
       </x:c>
       <x:c r="E143" s="8" t="str">
-        <x:v>[0]</x:v>
+        <x:v>[1]</x:v>
       </x:c>
       <x:c r="F143" s="8" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G143" s="8" t="str">
-        <x:v>決まります</x:v>
+        <x:v>混みます</x:v>
       </x:c>
       <x:c r="H143" s="8" t="str">
-        <x:v>決まって</x:v>
+        <x:v>混んで</x:v>
       </x:c>
       <x:c r="I143" s="9" t="str">
         <x:v>自</x:v>
@@ -7049,28 +6629,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B144" s="6" t="str">
-        <x:v>確かめる</x:v>
+        <x:v>決まる</x:v>
       </x:c>
       <x:c r="C144" s="6" t="str">
-        <x:v>たしかめる</x:v>
+        <x:v>きまる</x:v>
       </x:c>
       <x:c r="D144" s="7" t="str">
-        <x:v>确认、查明</x:v>
+        <x:v>定、决定</x:v>
       </x:c>
       <x:c r="E144" s="6" t="str">
-        <x:v>[4]</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F144" s="6" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G144" s="6" t="str">
-        <x:v>確かめます</x:v>
+        <x:v>決まります</x:v>
       </x:c>
       <x:c r="H144" s="6" t="str">
-        <x:v>確かめて</x:v>
+        <x:v>決まって</x:v>
       </x:c>
       <x:c r="I144" s="7" t="str">
-        <x:v>他</x:v>
+        <x:v>自</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="17">
@@ -7078,25 +6658,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B145" s="8" t="str">
-        <x:v>知らせる</x:v>
+        <x:v>確かめる</x:v>
       </x:c>
       <x:c r="C145" s="8" t="str">
-        <x:v>しらせる</x:v>
+        <x:v>たしかめる</x:v>
       </x:c>
       <x:c r="D145" s="9" t="str">
-        <x:v>告诉、通知</x:v>
+        <x:v>确认、查明</x:v>
       </x:c>
       <x:c r="E145" s="8" t="str">
-        <x:v>[0]</x:v>
+        <x:v>[4]</x:v>
       </x:c>
       <x:c r="F145" s="8" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G145" s="8" t="str">
-        <x:v>知らせます</x:v>
+        <x:v>確かめます</x:v>
       </x:c>
       <x:c r="H145" s="8" t="str">
-        <x:v>知らせて</x:v>
+        <x:v>確かめて</x:v>
       </x:c>
       <x:c r="I145" s="9" t="str">
         <x:v>他</x:v>
@@ -7104,28 +6684,28 @@
     </x:row>
     <x:row r="146" ht="17">
       <x:c r="A146" s="6" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B146" s="6" t="str">
-        <x:v>思う</x:v>
+        <x:v>知らせる</x:v>
       </x:c>
       <x:c r="C146" s="6" t="str">
-        <x:v>おもう</x:v>
+        <x:v>しらせる</x:v>
       </x:c>
       <x:c r="D146" s="7" t="str">
-        <x:v>想、思考、认为</x:v>
+        <x:v>告诉、通知</x:v>
       </x:c>
       <x:c r="E146" s="6" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F146" s="6" t="str">
-        <x:v>一类（五段）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G146" s="6" t="str">
-        <x:v>思います</x:v>
+        <x:v>知らせます</x:v>
       </x:c>
       <x:c r="H146" s="6" t="str">
-        <x:v>思って</x:v>
+        <x:v>知らせて</x:v>
       </x:c>
       <x:c r="I146" s="7" t="str">
         <x:v>他</x:v>
@@ -7136,13 +6716,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B147" s="8" t="str">
-        <x:v>言う</x:v>
+        <x:v>思う</x:v>
       </x:c>
       <x:c r="C147" s="8" t="str">
-        <x:v>いう</x:v>
+        <x:v>おもう</x:v>
       </x:c>
       <x:c r="D147" s="9" t="str">
-        <x:v>说、讲</x:v>
+        <x:v>想、思考、认为</x:v>
       </x:c>
       <x:c r="E147" s="8" t="str">
         <x:v>待核</x:v>
@@ -7151,13 +6731,13 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G147" s="8" t="str">
-        <x:v>言います</x:v>
+        <x:v>思います</x:v>
       </x:c>
       <x:c r="H147" s="8" t="str">
-        <x:v>言って</x:v>
+        <x:v>思って</x:v>
       </x:c>
       <x:c r="I147" s="9" t="str">
-        <x:v>他；第22课已出现</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="17">
@@ -7165,28 +6745,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B148" s="6" t="str">
-        <x:v>探す</x:v>
+        <x:v>言う</x:v>
       </x:c>
       <x:c r="C148" s="6" t="str">
-        <x:v>さがす</x:v>
+        <x:v>いう</x:v>
       </x:c>
       <x:c r="D148" s="7" t="str">
-        <x:v>找、寻找、寻求</x:v>
+        <x:v>说、讲</x:v>
       </x:c>
       <x:c r="E148" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F148" s="6" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G148" s="6" t="str">
-        <x:v>探します</x:v>
+        <x:v>言います</x:v>
       </x:c>
       <x:c r="H148" s="6" t="str">
-        <x:v>探して</x:v>
+        <x:v>言って</x:v>
       </x:c>
       <x:c r="I148" s="7" t="str">
-        <x:v>他</x:v>
+        <x:v>他；第22课已出现</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="17">
@@ -7194,13 +6774,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B149" s="8" t="str">
-        <x:v>笑う</x:v>
+        <x:v>探す</x:v>
       </x:c>
       <x:c r="C149" s="8" t="str">
-        <x:v>わらう</x:v>
+        <x:v>さがす</x:v>
       </x:c>
       <x:c r="D149" s="9" t="str">
-        <x:v>笑</x:v>
+        <x:v>找、寻找、寻求</x:v>
       </x:c>
       <x:c r="E149" s="8" t="str">
         <x:v>[0]</x:v>
@@ -7209,13 +6789,13 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G149" s="8" t="str">
-        <x:v>笑います</x:v>
+        <x:v>探します</x:v>
       </x:c>
       <x:c r="H149" s="8" t="str">
-        <x:v>笑って</x:v>
+        <x:v>探して</x:v>
       </x:c>
       <x:c r="I149" s="9" t="str">
-        <x:v>自/他视搭配</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="17">
@@ -7223,28 +6803,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B150" s="6" t="str">
-        <x:v>やめる</x:v>
+        <x:v>笑う</x:v>
       </x:c>
       <x:c r="C150" s="6" t="str">
-        <x:v>やめる</x:v>
+        <x:v>わらう</x:v>
       </x:c>
       <x:c r="D150" s="7" t="str">
-        <x:v>戒、停止、放弃；下班</x:v>
+        <x:v>笑</x:v>
       </x:c>
       <x:c r="E150" s="6" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F150" s="6" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G150" s="6" t="str">
-        <x:v>やめます</x:v>
+        <x:v>笑います</x:v>
       </x:c>
       <x:c r="H150" s="6" t="str">
-        <x:v>やめて</x:v>
+        <x:v>笑って</x:v>
       </x:c>
       <x:c r="I150" s="7" t="str">
-        <x:v>他/自视搭配</x:v>
+        <x:v>自/他视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="17">
@@ -7252,28 +6832,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B151" s="8" t="str">
-        <x:v>決める</x:v>
+        <x:v>やめる</x:v>
       </x:c>
       <x:c r="C151" s="8" t="str">
-        <x:v>きめる</x:v>
+        <x:v>やめる</x:v>
       </x:c>
       <x:c r="D151" s="9" t="str">
-        <x:v>决定</x:v>
+        <x:v>戒、停止、放弃；下班</x:v>
       </x:c>
       <x:c r="E151" s="8" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F151" s="8" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G151" s="8" t="str">
-        <x:v>決めます</x:v>
+        <x:v>やめます</x:v>
       </x:c>
       <x:c r="H151" s="8" t="str">
-        <x:v>決めて</x:v>
+        <x:v>やめて</x:v>
       </x:c>
       <x:c r="I151" s="9" t="str">
-        <x:v>他</x:v>
+        <x:v>他/自视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="17">
@@ -7281,28 +6861,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B152" s="6" t="str">
-        <x:v>研究する</x:v>
+        <x:v>決める</x:v>
       </x:c>
       <x:c r="C152" s="6" t="str">
-        <x:v>けんきゅうする</x:v>
+        <x:v>きめる</x:v>
       </x:c>
       <x:c r="D152" s="7" t="str">
-        <x:v>研究</x:v>
+        <x:v>决定</x:v>
       </x:c>
       <x:c r="E152" s="6" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F152" s="6" t="str">
-        <x:v>三类（サ变）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G152" s="6" t="str">
-        <x:v>研究します</x:v>
+        <x:v>決めます</x:v>
       </x:c>
       <x:c r="H152" s="6" t="str">
-        <x:v>研究して</x:v>
+        <x:v>決めて</x:v>
       </x:c>
       <x:c r="I152" s="7" t="str">
-        <x:v>他/自视搭配</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -7310,27 +6890,56 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B153" t="str">
-        <x:v>役に立つ</x:v>
+        <x:v>研究する</x:v>
       </x:c>
       <x:c r="C153" t="str">
-        <x:v>やくにたつ</x:v>
+        <x:v>けんきゅうする</x:v>
       </x:c>
       <x:c r="D153" t="str">
-        <x:v>起作用、有用</x:v>
+        <x:v>研究</x:v>
       </x:c>
       <x:c r="E153" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F153" t="str">
+        <x:v>三类（サ变）</x:v>
+      </x:c>
+      <x:c r="G153" t="str">
+        <x:v>研究します</x:v>
+      </x:c>
+      <x:c r="H153" t="str">
+        <x:v>研究して</x:v>
+      </x:c>
+      <x:c r="I153" t="str">
+        <x:v>他/自视搭配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>役に立つ</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>やくにたつ</x:v>
+      </x:c>
+      <x:c r="D154" t="str">
+        <x:v>起作用、有用</x:v>
+      </x:c>
+      <x:c r="E154" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F154" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
-      <x:c r="G153" t="str">
+      <x:c r="G154" t="str">
         <x:v>役に立ちます</x:v>
       </x:c>
-      <x:c r="H153" t="str">
+      <x:c r="H154" t="str">
         <x:v>役に立って</x:v>
       </x:c>
-      <x:c r="I153" t="str">
+      <x:c r="I154" t="str">
         <x:v>自；词组动词</x:v>
       </x:c>
     </x:row>
@@ -7349,78 +6958,78 @@
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>654</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
     </x:row>
     <x:row r="2" ht="17">
       <x:c r="A2" s="2" t="s">
-        <x:v>655</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
     </x:row>
     <x:row r="3" ht="34">
       <x:c r="A3" s="2" t="s">
-        <x:v>656</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="B3" s="3" t="s">
-        <x:v>657</x:v>
+        <x:v>517</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="17">
       <x:c r="A4" s="2" t="s">
-        <x:v>658</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="B4" s="3" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="17">
       <x:c r="A5" s="2" t="s">
-        <x:v>659</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="B5" s="3" t="n">
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34">
       <x:c r="A6" s="2" t="s">
-        <x:v>660</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>661</x:v>
+        <x:v>521</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34">
       <x:c r="A7" s="2" t="s">
-        <x:v>662</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>663</x:v>
+        <x:v>523</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34">
       <x:c r="A8" s="2" t="s">
-        <x:v>664</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>665</x:v>
+        <x:v>525</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34">
       <x:c r="A9" s="2" t="s">
-        <x:v>666</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="B9" s="3" t="s">
-        <x:v>667</x:v>
+        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34">
       <x:c r="A10" s="2" t="s">
-        <x:v>668</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>669</x:v>
+        <x:v>529</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -7428,7 +7037,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B12" t="s">
-        <x:v>670</x:v>
+        <x:v>530</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -7547,8 +7156,8 @@
       <x:c r="A27">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B27">
-        <x:v>3</x:v>
+      <x:c r="B27" t="n">
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -7601,11 +7210,11 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="4" t="s">
-        <x:v>671</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="B34" s="4" t="n">
         <x:f ca="1">SUM(B13:B33)</x:f>
-        <x:v>152</x:v>
+        <x:v>153</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/doc/新标日初级上册动词表.xlsx
+++ b/doc/新标日初级上册动词表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动词表" sheetId="1" r:id="R8889f620ad3e47ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="Rd188cf04b5df4041"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动词表" sheetId="1" r:id="R1327f9cc718449f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="R8604ee14fc624338"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -6452,31 +6452,31 @@
     </x:row>
     <x:row r="138" ht="17">
       <x:c r="A138" s="6" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B138" s="6" t="str">
-        <x:v>見る</x:v>
+        <x:v>報告する</x:v>
       </x:c>
       <x:c r="C138" s="6" t="str">
-        <x:v>みる</x:v>
+        <x:v>ほうこくする</x:v>
       </x:c>
       <x:c r="D138" s="7" t="str">
-        <x:v>看、观看</x:v>
+        <x:v>报告、汇报</x:v>
       </x:c>
       <x:c r="E138" s="6" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F138" s="6" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>三类（サ变）</x:v>
       </x:c>
       <x:c r="G138" s="6" t="str">
-        <x:v>見ます</x:v>
+        <x:v>報告します</x:v>
       </x:c>
       <x:c r="H138" s="6" t="str">
-        <x:v>見て</x:v>
+        <x:v>報告して</x:v>
       </x:c>
       <x:c r="I138" s="7" t="str">
-        <x:v>他；第7课已出现，语法例句复用</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="17">
@@ -6484,28 +6484,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B139" s="8" t="str">
-        <x:v>する</x:v>
+        <x:v>見る</x:v>
       </x:c>
       <x:c r="C139" s="8" t="str">
-        <x:v>する</x:v>
+        <x:v>みる</x:v>
       </x:c>
       <x:c r="D139" s="9" t="str">
-        <x:v>做、干</x:v>
+        <x:v>看、观看</x:v>
       </x:c>
       <x:c r="E139" s="8" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F139" s="8" t="str">
-        <x:v>三类（サ变）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G139" s="8" t="str">
-        <x:v>します</x:v>
+        <x:v>見ます</x:v>
       </x:c>
       <x:c r="H139" s="8" t="str">
-        <x:v>して</x:v>
+        <x:v>見て</x:v>
       </x:c>
       <x:c r="I139" s="9" t="str">
-        <x:v>第7课已出现</x:v>
+        <x:v>他；第7课已出现，语法例句复用</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="17">
@@ -6513,28 +6513,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B140" s="6" t="str">
-        <x:v>言う</x:v>
+        <x:v>する</x:v>
       </x:c>
       <x:c r="C140" s="6" t="str">
-        <x:v>いう</x:v>
+        <x:v>する</x:v>
       </x:c>
       <x:c r="D140" s="7" t="str">
-        <x:v>说、讲</x:v>
+        <x:v>做、干</x:v>
       </x:c>
       <x:c r="E140" s="6" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F140" s="6" t="str">
-        <x:v>一类（五段）</x:v>
+        <x:v>三类（サ变）</x:v>
       </x:c>
       <x:c r="G140" s="6" t="str">
-        <x:v>言います</x:v>
+        <x:v>します</x:v>
       </x:c>
       <x:c r="H140" s="6" t="str">
-        <x:v>言って</x:v>
+        <x:v>して</x:v>
       </x:c>
       <x:c r="I140" s="7" t="str">
-        <x:v>他</x:v>
+        <x:v>第7课已出现</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="17">
@@ -6542,13 +6542,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B141" s="8" t="str">
-        <x:v>帰る</x:v>
+        <x:v>言う</x:v>
       </x:c>
       <x:c r="C141" s="8" t="str">
-        <x:v>かえる</x:v>
+        <x:v>いう</x:v>
       </x:c>
       <x:c r="D141" s="9" t="str">
-        <x:v>回、回去</x:v>
+        <x:v>说、讲</x:v>
       </x:c>
       <x:c r="E141" s="8" t="str">
         <x:v>待核</x:v>
@@ -6557,42 +6557,42 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G141" s="8" t="str">
-        <x:v>帰ります</x:v>
+        <x:v>言います</x:v>
       </x:c>
       <x:c r="H141" s="8" t="str">
-        <x:v>帰って</x:v>
+        <x:v>言って</x:v>
       </x:c>
       <x:c r="I141" s="9" t="str">
-        <x:v>自；第6课已出现</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="17">
       <x:c r="A142" s="6" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B142" s="6" t="str">
-        <x:v>違う</x:v>
+        <x:v>帰る</x:v>
       </x:c>
       <x:c r="C142" s="6" t="str">
-        <x:v>ちがう</x:v>
+        <x:v>かえる</x:v>
       </x:c>
       <x:c r="D142" s="7" t="str">
-        <x:v>不同、不一样</x:v>
+        <x:v>回、回去</x:v>
       </x:c>
       <x:c r="E142" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F142" s="6" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G142" s="6" t="str">
-        <x:v>違います</x:v>
+        <x:v>帰ります</x:v>
       </x:c>
       <x:c r="H142" s="6" t="str">
-        <x:v>違って</x:v>
+        <x:v>帰って</x:v>
       </x:c>
       <x:c r="I142" s="7" t="str">
-        <x:v>自</x:v>
+        <x:v>自；第6课已出现</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="17">
@@ -6600,25 +6600,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B143" s="8" t="str">
-        <x:v>混む</x:v>
+        <x:v>違う</x:v>
       </x:c>
       <x:c r="C143" s="8" t="str">
-        <x:v>こむ</x:v>
+        <x:v>ちがう</x:v>
       </x:c>
       <x:c r="D143" s="9" t="str">
-        <x:v>拥挤、混杂</x:v>
+        <x:v>不同、不一样</x:v>
       </x:c>
       <x:c r="E143" s="8" t="str">
-        <x:v>[1]</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F143" s="8" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G143" s="8" t="str">
-        <x:v>混みます</x:v>
+        <x:v>違います</x:v>
       </x:c>
       <x:c r="H143" s="8" t="str">
-        <x:v>混んで</x:v>
+        <x:v>違って</x:v>
       </x:c>
       <x:c r="I143" s="9" t="str">
         <x:v>自</x:v>
@@ -6629,25 +6629,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B144" s="6" t="str">
-        <x:v>決まる</x:v>
+        <x:v>混む</x:v>
       </x:c>
       <x:c r="C144" s="6" t="str">
-        <x:v>きまる</x:v>
+        <x:v>こむ</x:v>
       </x:c>
       <x:c r="D144" s="7" t="str">
-        <x:v>定、决定</x:v>
+        <x:v>拥挤、混杂</x:v>
       </x:c>
       <x:c r="E144" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>[1]</x:v>
       </x:c>
       <x:c r="F144" s="6" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G144" s="6" t="str">
-        <x:v>決まります</x:v>
+        <x:v>混みます</x:v>
       </x:c>
       <x:c r="H144" s="6" t="str">
-        <x:v>決まって</x:v>
+        <x:v>混んで</x:v>
       </x:c>
       <x:c r="I144" s="7" t="str">
         <x:v>自</x:v>
@@ -6658,28 +6658,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B145" s="8" t="str">
-        <x:v>確かめる</x:v>
+        <x:v>決まる</x:v>
       </x:c>
       <x:c r="C145" s="8" t="str">
-        <x:v>たしかめる</x:v>
+        <x:v>きまる</x:v>
       </x:c>
       <x:c r="D145" s="9" t="str">
-        <x:v>确认、查明</x:v>
+        <x:v>定、决定</x:v>
       </x:c>
       <x:c r="E145" s="8" t="str">
-        <x:v>[4]</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F145" s="8" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G145" s="8" t="str">
-        <x:v>確かめます</x:v>
+        <x:v>決まります</x:v>
       </x:c>
       <x:c r="H145" s="8" t="str">
-        <x:v>確かめて</x:v>
+        <x:v>決まって</x:v>
       </x:c>
       <x:c r="I145" s="9" t="str">
-        <x:v>他</x:v>
+        <x:v>自</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="17">
@@ -6687,25 +6687,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B146" s="6" t="str">
-        <x:v>知らせる</x:v>
+        <x:v>確かめる</x:v>
       </x:c>
       <x:c r="C146" s="6" t="str">
-        <x:v>しらせる</x:v>
+        <x:v>たしかめる</x:v>
       </x:c>
       <x:c r="D146" s="7" t="str">
-        <x:v>告诉、通知</x:v>
+        <x:v>确认、查明</x:v>
       </x:c>
       <x:c r="E146" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>[4]</x:v>
       </x:c>
       <x:c r="F146" s="6" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G146" s="6" t="str">
-        <x:v>知らせます</x:v>
+        <x:v>確かめます</x:v>
       </x:c>
       <x:c r="H146" s="6" t="str">
-        <x:v>知らせて</x:v>
+        <x:v>確かめて</x:v>
       </x:c>
       <x:c r="I146" s="7" t="str">
         <x:v>他</x:v>
@@ -6713,28 +6713,28 @@
     </x:row>
     <x:row r="147" ht="17">
       <x:c r="A147" s="8" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B147" s="8" t="str">
-        <x:v>思う</x:v>
+        <x:v>知らせる</x:v>
       </x:c>
       <x:c r="C147" s="8" t="str">
-        <x:v>おもう</x:v>
+        <x:v>しらせる</x:v>
       </x:c>
       <x:c r="D147" s="9" t="str">
-        <x:v>想、思考、认为</x:v>
+        <x:v>告诉、通知</x:v>
       </x:c>
       <x:c r="E147" s="8" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F147" s="8" t="str">
-        <x:v>一类（五段）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G147" s="8" t="str">
-        <x:v>思います</x:v>
+        <x:v>知らせます</x:v>
       </x:c>
       <x:c r="H147" s="8" t="str">
-        <x:v>思って</x:v>
+        <x:v>知らせて</x:v>
       </x:c>
       <x:c r="I147" s="9" t="str">
         <x:v>他</x:v>
@@ -6745,13 +6745,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B148" s="6" t="str">
-        <x:v>言う</x:v>
+        <x:v>思う</x:v>
       </x:c>
       <x:c r="C148" s="6" t="str">
-        <x:v>いう</x:v>
+        <x:v>おもう</x:v>
       </x:c>
       <x:c r="D148" s="7" t="str">
-        <x:v>说、讲</x:v>
+        <x:v>想、思考、认为</x:v>
       </x:c>
       <x:c r="E148" s="6" t="str">
         <x:v>待核</x:v>
@@ -6760,13 +6760,13 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G148" s="6" t="str">
-        <x:v>言います</x:v>
+        <x:v>思います</x:v>
       </x:c>
       <x:c r="H148" s="6" t="str">
-        <x:v>言って</x:v>
+        <x:v>思って</x:v>
       </x:c>
       <x:c r="I148" s="7" t="str">
-        <x:v>他；第22课已出现</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="17">
@@ -6774,28 +6774,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B149" s="8" t="str">
-        <x:v>探す</x:v>
+        <x:v>言う</x:v>
       </x:c>
       <x:c r="C149" s="8" t="str">
-        <x:v>さがす</x:v>
+        <x:v>いう</x:v>
       </x:c>
       <x:c r="D149" s="9" t="str">
-        <x:v>找、寻找、寻求</x:v>
+        <x:v>说、讲</x:v>
       </x:c>
       <x:c r="E149" s="8" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F149" s="8" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G149" s="8" t="str">
-        <x:v>探します</x:v>
+        <x:v>言います</x:v>
       </x:c>
       <x:c r="H149" s="8" t="str">
-        <x:v>探して</x:v>
+        <x:v>言って</x:v>
       </x:c>
       <x:c r="I149" s="9" t="str">
-        <x:v>他</x:v>
+        <x:v>他；第22课已出现</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="17">
@@ -6803,13 +6803,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B150" s="6" t="str">
-        <x:v>笑う</x:v>
+        <x:v>探す</x:v>
       </x:c>
       <x:c r="C150" s="6" t="str">
-        <x:v>わらう</x:v>
+        <x:v>さがす</x:v>
       </x:c>
       <x:c r="D150" s="7" t="str">
-        <x:v>笑</x:v>
+        <x:v>找、寻找、寻求</x:v>
       </x:c>
       <x:c r="E150" s="6" t="str">
         <x:v>[0]</x:v>
@@ -6818,13 +6818,13 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G150" s="6" t="str">
-        <x:v>笑います</x:v>
+        <x:v>探します</x:v>
       </x:c>
       <x:c r="H150" s="6" t="str">
-        <x:v>笑って</x:v>
+        <x:v>探して</x:v>
       </x:c>
       <x:c r="I150" s="7" t="str">
-        <x:v>自/他视搭配</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="17">
@@ -6832,28 +6832,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B151" s="8" t="str">
-        <x:v>やめる</x:v>
+        <x:v>笑う</x:v>
       </x:c>
       <x:c r="C151" s="8" t="str">
-        <x:v>やめる</x:v>
+        <x:v>わらう</x:v>
       </x:c>
       <x:c r="D151" s="9" t="str">
-        <x:v>戒、停止、放弃；下班</x:v>
+        <x:v>笑</x:v>
       </x:c>
       <x:c r="E151" s="8" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F151" s="8" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G151" s="8" t="str">
-        <x:v>やめます</x:v>
+        <x:v>笑います</x:v>
       </x:c>
       <x:c r="H151" s="8" t="str">
-        <x:v>やめて</x:v>
+        <x:v>笑って</x:v>
       </x:c>
       <x:c r="I151" s="9" t="str">
-        <x:v>他/自视搭配</x:v>
+        <x:v>自/他视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="17">
@@ -6861,28 +6861,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B152" s="6" t="str">
-        <x:v>決める</x:v>
+        <x:v>やめる</x:v>
       </x:c>
       <x:c r="C152" s="6" t="str">
-        <x:v>きめる</x:v>
+        <x:v>やめる</x:v>
       </x:c>
       <x:c r="D152" s="7" t="str">
-        <x:v>决定</x:v>
+        <x:v>戒、停止、放弃；下班</x:v>
       </x:c>
       <x:c r="E152" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F152" s="6" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G152" s="6" t="str">
-        <x:v>決めます</x:v>
+        <x:v>やめます</x:v>
       </x:c>
       <x:c r="H152" s="6" t="str">
-        <x:v>決めて</x:v>
+        <x:v>やめて</x:v>
       </x:c>
       <x:c r="I152" s="7" t="str">
-        <x:v>他</x:v>
+        <x:v>他/自视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -6890,28 +6890,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B153" t="str">
-        <x:v>研究する</x:v>
+        <x:v>決める</x:v>
       </x:c>
       <x:c r="C153" t="str">
-        <x:v>けんきゅうする</x:v>
+        <x:v>きめる</x:v>
       </x:c>
       <x:c r="D153" t="str">
-        <x:v>研究</x:v>
+        <x:v>决定</x:v>
       </x:c>
       <x:c r="E153" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F153" t="str">
-        <x:v>三类（サ变）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G153" t="str">
-        <x:v>研究します</x:v>
+        <x:v>決めます</x:v>
       </x:c>
       <x:c r="H153" t="str">
-        <x:v>研究して</x:v>
+        <x:v>決めて</x:v>
       </x:c>
       <x:c r="I153" t="str">
-        <x:v>他/自视搭配</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -6919,27 +6919,56 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B154" t="str">
-        <x:v>役に立つ</x:v>
+        <x:v>研究する</x:v>
       </x:c>
       <x:c r="C154" t="str">
-        <x:v>やくにたつ</x:v>
+        <x:v>けんきゅうする</x:v>
       </x:c>
       <x:c r="D154" t="str">
-        <x:v>起作用、有用</x:v>
+        <x:v>研究</x:v>
       </x:c>
       <x:c r="E154" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F154" t="str">
+        <x:v>三类（サ变）</x:v>
+      </x:c>
+      <x:c r="G154" t="str">
+        <x:v>研究します</x:v>
+      </x:c>
+      <x:c r="H154" t="str">
+        <x:v>研究して</x:v>
+      </x:c>
+      <x:c r="I154" t="str">
+        <x:v>他/自视搭配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>役に立つ</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>やくにたつ</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
+        <x:v>起作用、有用</x:v>
+      </x:c>
+      <x:c r="E155" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F155" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
-      <x:c r="G154" t="str">
+      <x:c r="G155" t="str">
         <x:v>役に立ちます</x:v>
       </x:c>
-      <x:c r="H154" t="str">
+      <x:c r="H155" t="str">
         <x:v>役に立って</x:v>
       </x:c>
-      <x:c r="I154" t="str">
+      <x:c r="I155" t="str">
         <x:v>自；词组动词</x:v>
       </x:c>
     </x:row>
@@ -6981,7 +7010,7 @@
         <x:v>518</x:v>
       </x:c>
       <x:c r="B4" s="3" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="17">
@@ -6989,7 +7018,7 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B5" s="3" t="n">
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34">
@@ -7181,7 +7210,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B30" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -7214,7 +7243,7 @@
       </x:c>
       <x:c r="B34" s="4" t="n">
         <x:f ca="1">SUM(B13:B33)</x:f>
-        <x:v>153</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/doc/新标日初级上册动词表.xlsx
+++ b/doc/新标日初级上册动词表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动词表" sheetId="1" r:id="R1327f9cc718449f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="R8604ee14fc624338"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动词表" sheetId="1" r:id="R3691361244bf402a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="R9045fe83439247d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5904,25 +5904,25 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B119" s="8" t="str">
-        <x:v>落とす</x:v>
+        <x:v>なくす</x:v>
       </x:c>
       <x:c r="C119" s="8" t="str">
-        <x:v>おとす</x:v>
+        <x:v>なくす</x:v>
       </x:c>
       <x:c r="D119" s="9" t="str">
-        <x:v>丢、丢失；弄掉</x:v>
+        <x:v>丢、丢失</x:v>
       </x:c>
       <x:c r="E119" s="8" t="str">
-        <x:v>[2]</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F119" s="8" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G119" s="8" t="str">
-        <x:v>落とします</x:v>
+        <x:v>なくします</x:v>
       </x:c>
       <x:c r="H119" s="8" t="str">
-        <x:v>落として</x:v>
+        <x:v>なくして</x:v>
       </x:c>
       <x:c r="I119" s="9" t="str">
         <x:v>他</x:v>
@@ -5933,28 +5933,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B120" s="6" t="str">
-        <x:v>置く</x:v>
+        <x:v>落とす</x:v>
       </x:c>
       <x:c r="C120" s="6" t="str">
-        <x:v>おく</x:v>
+        <x:v>おとす</x:v>
       </x:c>
       <x:c r="D120" s="7" t="str">
-        <x:v>放置</x:v>
+        <x:v>丢、丢失；弄掉</x:v>
       </x:c>
       <x:c r="E120" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>[2]</x:v>
       </x:c>
       <x:c r="F120" s="6" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G120" s="6" t="str">
-        <x:v>置きます</x:v>
+        <x:v>落とします</x:v>
       </x:c>
       <x:c r="H120" s="6" t="str">
-        <x:v>置いて</x:v>
+        <x:v>落として</x:v>
       </x:c>
       <x:c r="I120" s="7" t="str">
-        <x:v>他；い音便</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="17">
@@ -5962,28 +5962,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B121" s="8" t="str">
-        <x:v>払う</x:v>
+        <x:v>置く</x:v>
       </x:c>
       <x:c r="C121" s="8" t="str">
-        <x:v>はらう</x:v>
+        <x:v>おく</x:v>
       </x:c>
       <x:c r="D121" s="9" t="str">
-        <x:v>支付</x:v>
+        <x:v>放置</x:v>
       </x:c>
       <x:c r="E121" s="8" t="str">
-        <x:v>[2]</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F121" s="8" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G121" s="8" t="str">
-        <x:v>払います</x:v>
+        <x:v>置きます</x:v>
       </x:c>
       <x:c r="H121" s="8" t="str">
-        <x:v>払って</x:v>
+        <x:v>置いて</x:v>
       </x:c>
       <x:c r="I121" s="9" t="str">
-        <x:v>他</x:v>
+        <x:v>他；い音便</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="17">
@@ -5991,28 +5991,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B122" s="6" t="str">
-        <x:v>立つ</x:v>
+        <x:v>払う</x:v>
       </x:c>
       <x:c r="C122" s="6" t="str">
-        <x:v>たつ</x:v>
+        <x:v>はらう</x:v>
       </x:c>
       <x:c r="D122" s="7" t="str">
-        <x:v>站、立</x:v>
+        <x:v>支付</x:v>
       </x:c>
       <x:c r="E122" s="6" t="str">
-        <x:v>[1]</x:v>
+        <x:v>[2]</x:v>
       </x:c>
       <x:c r="F122" s="6" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G122" s="6" t="str">
-        <x:v>立ちます</x:v>
+        <x:v>払います</x:v>
       </x:c>
       <x:c r="H122" s="6" t="str">
-        <x:v>立って</x:v>
+        <x:v>払って</x:v>
       </x:c>
       <x:c r="I122" s="7" t="str">
-        <x:v>自</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="17">
@@ -6020,28 +6020,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B123" s="8" t="str">
-        <x:v>忘れる</x:v>
+        <x:v>立つ</x:v>
       </x:c>
       <x:c r="C123" s="8" t="str">
-        <x:v>わすれる</x:v>
+        <x:v>たつ</x:v>
       </x:c>
       <x:c r="D123" s="9" t="str">
-        <x:v>忘记</x:v>
+        <x:v>站、立</x:v>
       </x:c>
       <x:c r="E123" s="8" t="str">
-        <x:v>待核</x:v>
+        <x:v>[1]</x:v>
       </x:c>
       <x:c r="F123" s="8" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G123" s="8" t="str">
-        <x:v>忘れます</x:v>
+        <x:v>立ちます</x:v>
       </x:c>
       <x:c r="H123" s="8" t="str">
-        <x:v>忘れて</x:v>
+        <x:v>立って</x:v>
       </x:c>
       <x:c r="I123" s="9" t="str">
-        <x:v>他</x:v>
+        <x:v>自</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="17">
@@ -6049,28 +6049,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B124" s="6" t="str">
-        <x:v>慌てる</x:v>
+        <x:v>忘れる</x:v>
       </x:c>
       <x:c r="C124" s="6" t="str">
-        <x:v>あわてる</x:v>
+        <x:v>わすれる</x:v>
       </x:c>
       <x:c r="D124" s="7" t="str">
-        <x:v>慌张、惊慌、着急</x:v>
+        <x:v>忘记</x:v>
       </x:c>
       <x:c r="E124" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F124" s="6" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G124" s="6" t="str">
-        <x:v>慌てます</x:v>
+        <x:v>忘れます</x:v>
       </x:c>
       <x:c r="H124" s="6" t="str">
-        <x:v>慌てて</x:v>
+        <x:v>忘れて</x:v>
       </x:c>
       <x:c r="I124" s="7" t="str">
-        <x:v>自/他视搭配</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="17">
@@ -6078,13 +6078,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B125" s="8" t="str">
-        <x:v>捨てる</x:v>
+        <x:v>慌てる</x:v>
       </x:c>
       <x:c r="C125" s="8" t="str">
-        <x:v>すてる</x:v>
+        <x:v>あわてる</x:v>
       </x:c>
       <x:c r="D125" s="9" t="str">
-        <x:v>扔、扔掉</x:v>
+        <x:v>慌张、惊慌、着急</x:v>
       </x:c>
       <x:c r="E125" s="8" t="str">
         <x:v>[0]</x:v>
@@ -6093,13 +6093,13 @@
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G125" s="8" t="str">
-        <x:v>捨てます</x:v>
+        <x:v>慌てます</x:v>
       </x:c>
       <x:c r="H125" s="8" t="str">
-        <x:v>捨てて</x:v>
+        <x:v>慌てて</x:v>
       </x:c>
       <x:c r="I125" s="9" t="str">
-        <x:v>他</x:v>
+        <x:v>自/他视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="17">
@@ -6107,28 +6107,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B126" s="6" t="str">
-        <x:v>残業する</x:v>
+        <x:v>捨てる</x:v>
       </x:c>
       <x:c r="C126" s="6" t="str">
-        <x:v>ざんぎょうする</x:v>
+        <x:v>すてる</x:v>
       </x:c>
       <x:c r="D126" s="7" t="str">
-        <x:v>加班</x:v>
+        <x:v>扔、扔掉</x:v>
       </x:c>
       <x:c r="E126" s="6" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F126" s="6" t="str">
-        <x:v>三类（サ变）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G126" s="6" t="str">
-        <x:v>残業します</x:v>
+        <x:v>捨てます</x:v>
       </x:c>
       <x:c r="H126" s="6" t="str">
-        <x:v>残業して</x:v>
+        <x:v>捨てて</x:v>
       </x:c>
       <x:c r="I126" s="7" t="str">
-        <x:v>自</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="17">
@@ -6136,13 +6136,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B127" s="8" t="str">
-        <x:v>心配する</x:v>
+        <x:v>残業する</x:v>
       </x:c>
       <x:c r="C127" s="8" t="str">
-        <x:v>しんぱいする</x:v>
+        <x:v>ざんぎょうする</x:v>
       </x:c>
       <x:c r="D127" s="9" t="str">
-        <x:v>担心、挂念</x:v>
+        <x:v>加班</x:v>
       </x:c>
       <x:c r="E127" s="8" t="str">
         <x:v>待核</x:v>
@@ -6151,42 +6151,42 @@
         <x:v>三类（サ变）</x:v>
       </x:c>
       <x:c r="G127" s="8" t="str">
-        <x:v>心配します</x:v>
+        <x:v>残業します</x:v>
       </x:c>
       <x:c r="H127" s="8" t="str">
-        <x:v>心配して</x:v>
+        <x:v>残業して</x:v>
       </x:c>
       <x:c r="I127" s="9" t="str">
-        <x:v>自/他视搭配</x:v>
+        <x:v>自</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="17">
       <x:c r="A128" s="6" t="n">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B128" s="6" t="str">
-        <x:v>浴びる</x:v>
+        <x:v>心配する</x:v>
       </x:c>
       <x:c r="C128" s="6" t="str">
-        <x:v>あびる</x:v>
+        <x:v>しんぱいする</x:v>
       </x:c>
       <x:c r="D128" s="7" t="str">
-        <x:v>淋、浇、沐浴</x:v>
+        <x:v>担心、挂念</x:v>
       </x:c>
       <x:c r="E128" s="6" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F128" s="6" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>三类（サ变）</x:v>
       </x:c>
       <x:c r="G128" s="6" t="str">
-        <x:v>浴びます</x:v>
+        <x:v>心配します</x:v>
       </x:c>
       <x:c r="H128" s="6" t="str">
-        <x:v>浴びて</x:v>
+        <x:v>心配して</x:v>
       </x:c>
       <x:c r="I128" s="7" t="str">
-        <x:v>他</x:v>
+        <x:v>自/他视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="17">
@@ -6194,25 +6194,25 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B129" s="8" t="str">
-        <x:v>集める</x:v>
+        <x:v>浴びる</x:v>
       </x:c>
       <x:c r="C129" s="8" t="str">
-        <x:v>あつめる</x:v>
+        <x:v>あびる</x:v>
       </x:c>
       <x:c r="D129" s="9" t="str">
-        <x:v>收集</x:v>
+        <x:v>淋、浇、沐浴</x:v>
       </x:c>
       <x:c r="E129" s="8" t="str">
-        <x:v>[3]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F129" s="8" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G129" s="8" t="str">
-        <x:v>集めます</x:v>
+        <x:v>浴びます</x:v>
       </x:c>
       <x:c r="H129" s="8" t="str">
-        <x:v>集めて</x:v>
+        <x:v>浴びて</x:v>
       </x:c>
       <x:c r="I129" s="9" t="str">
         <x:v>他</x:v>
@@ -6223,28 +6223,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B130" s="6" t="str">
-        <x:v>登る</x:v>
+        <x:v>集める</x:v>
       </x:c>
       <x:c r="C130" s="6" t="str">
-        <x:v>のぼる</x:v>
+        <x:v>あつめる</x:v>
       </x:c>
       <x:c r="D130" s="7" t="str">
-        <x:v>登、上</x:v>
+        <x:v>收集</x:v>
       </x:c>
       <x:c r="E130" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>[3]</x:v>
       </x:c>
       <x:c r="F130" s="6" t="str">
-        <x:v>一类（五段）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G130" s="6" t="str">
-        <x:v>登ります</x:v>
+        <x:v>集めます</x:v>
       </x:c>
       <x:c r="H130" s="6" t="str">
-        <x:v>登って</x:v>
+        <x:v>集めて</x:v>
       </x:c>
       <x:c r="I130" s="7" t="str">
-        <x:v>自/他视搭配</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="17">
@@ -6252,13 +6252,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B131" s="8" t="str">
-        <x:v>弾く</x:v>
+        <x:v>登る</x:v>
       </x:c>
       <x:c r="C131" s="8" t="str">
-        <x:v>ひく</x:v>
+        <x:v>のぼる</x:v>
       </x:c>
       <x:c r="D131" s="9" t="str">
-        <x:v>弹（琴等）</x:v>
+        <x:v>登、上</x:v>
       </x:c>
       <x:c r="E131" s="8" t="str">
         <x:v>[0]</x:v>
@@ -6267,42 +6267,42 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G131" s="8" t="str">
-        <x:v>弾きます</x:v>
+        <x:v>登ります</x:v>
       </x:c>
       <x:c r="H131" s="8" t="str">
-        <x:v>弾いて</x:v>
+        <x:v>登って</x:v>
       </x:c>
       <x:c r="I131" s="9" t="str">
-        <x:v>他；い音便</x:v>
+        <x:v>自/他视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="17">
       <x:c r="A132" s="6" t="n">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B132" s="6" t="str">
-        <x:v>洗濯する</x:v>
+        <x:v>弾く</x:v>
       </x:c>
       <x:c r="C132" s="6" t="str">
-        <x:v>せんたくする</x:v>
+        <x:v>ひく</x:v>
       </x:c>
       <x:c r="D132" s="7" t="str">
-        <x:v>洗涤、洗衣服</x:v>
+        <x:v>弹（琴等）</x:v>
       </x:c>
       <x:c r="E132" s="6" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F132" s="6" t="str">
-        <x:v>三类（サ变）</x:v>
+        <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G132" s="6" t="str">
-        <x:v>洗濯します</x:v>
+        <x:v>弾きます</x:v>
       </x:c>
       <x:c r="H132" s="6" t="str">
-        <x:v>洗濯して</x:v>
+        <x:v>弾いて</x:v>
       </x:c>
       <x:c r="I132" s="7" t="str">
-        <x:v>他</x:v>
+        <x:v>他；い音便</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="17">
@@ -6310,13 +6310,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B133" s="8" t="str">
-        <x:v>予約する</x:v>
+        <x:v>洗濯する</x:v>
       </x:c>
       <x:c r="C133" s="8" t="str">
-        <x:v>よやくする</x:v>
+        <x:v>せんたくする</x:v>
       </x:c>
       <x:c r="D133" s="9" t="str">
-        <x:v>预约</x:v>
+        <x:v>洗涤、洗衣服</x:v>
       </x:c>
       <x:c r="E133" s="8" t="str">
         <x:v>待核</x:v>
@@ -6325,10 +6325,10 @@
         <x:v>三类（サ变）</x:v>
       </x:c>
       <x:c r="G133" s="8" t="str">
-        <x:v>予約します</x:v>
+        <x:v>洗濯します</x:v>
       </x:c>
       <x:c r="H133" s="8" t="str">
-        <x:v>予約して</x:v>
+        <x:v>洗濯して</x:v>
       </x:c>
       <x:c r="I133" s="9" t="str">
         <x:v>他</x:v>
@@ -6339,25 +6339,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B134" s="6" t="str">
-        <x:v>着る</x:v>
+        <x:v>予約する</x:v>
       </x:c>
       <x:c r="C134" s="6" t="str">
-        <x:v>きる</x:v>
+        <x:v>よやくする</x:v>
       </x:c>
       <x:c r="D134" s="7" t="str">
-        <x:v>穿（上衣）</x:v>
+        <x:v>预约</x:v>
       </x:c>
       <x:c r="E134" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F134" s="6" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>三类（サ变）</x:v>
       </x:c>
       <x:c r="G134" s="6" t="str">
-        <x:v>着ます</x:v>
+        <x:v>予約します</x:v>
       </x:c>
       <x:c r="H134" s="6" t="str">
-        <x:v>着て</x:v>
+        <x:v>予約して</x:v>
       </x:c>
       <x:c r="I134" s="7" t="str">
         <x:v>他</x:v>
@@ -6368,25 +6368,25 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B135" s="8" t="str">
-        <x:v>調べる</x:v>
+        <x:v>着る</x:v>
       </x:c>
       <x:c r="C135" s="8" t="str">
-        <x:v>しらべる</x:v>
+        <x:v>きる</x:v>
       </x:c>
       <x:c r="D135" s="9" t="str">
-        <x:v>调查、查（看）、弄清</x:v>
+        <x:v>穿（上衣）</x:v>
       </x:c>
       <x:c r="E135" s="8" t="str">
-        <x:v>[3]</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F135" s="8" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G135" s="8" t="str">
-        <x:v>調べます</x:v>
+        <x:v>着ます</x:v>
       </x:c>
       <x:c r="H135" s="8" t="str">
-        <x:v>調べて</x:v>
+        <x:v>着て</x:v>
       </x:c>
       <x:c r="I135" s="9" t="str">
         <x:v>他</x:v>
@@ -6397,28 +6397,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B136" s="6" t="str">
-        <x:v>考える</x:v>
+        <x:v>調べる</x:v>
       </x:c>
       <x:c r="C136" s="6" t="str">
-        <x:v>かんがえる</x:v>
+        <x:v>しらべる</x:v>
       </x:c>
       <x:c r="D136" s="7" t="str">
-        <x:v>考虑、思考</x:v>
+        <x:v>调查、查（看）、弄清</x:v>
       </x:c>
       <x:c r="E136" s="6" t="str">
-        <x:v>待核</x:v>
+        <x:v>[3]</x:v>
       </x:c>
       <x:c r="F136" s="6" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G136" s="6" t="str">
-        <x:v>考えます</x:v>
+        <x:v>調べます</x:v>
       </x:c>
       <x:c r="H136" s="6" t="str">
-        <x:v>考えて</x:v>
+        <x:v>調べて</x:v>
       </x:c>
       <x:c r="I136" s="7" t="str">
-        <x:v>他/自视搭配</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="17">
@@ -6426,28 +6426,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B137" s="8" t="str">
-        <x:v>遅れる</x:v>
+        <x:v>考える</x:v>
       </x:c>
       <x:c r="C137" s="8" t="str">
-        <x:v>おくれる</x:v>
+        <x:v>かんがえる</x:v>
       </x:c>
       <x:c r="D137" s="9" t="str">
-        <x:v>迟到、晚</x:v>
+        <x:v>考虑、思考</x:v>
       </x:c>
       <x:c r="E137" s="8" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F137" s="8" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G137" s="8" t="str">
-        <x:v>遅れます</x:v>
+        <x:v>考えます</x:v>
       </x:c>
       <x:c r="H137" s="8" t="str">
-        <x:v>遅れて</x:v>
+        <x:v>考えて</x:v>
       </x:c>
       <x:c r="I137" s="9" t="str">
-        <x:v>自</x:v>
+        <x:v>他/自视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="17">
@@ -6455,57 +6455,57 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B138" s="6" t="str">
-        <x:v>報告する</x:v>
+        <x:v>遅れる</x:v>
       </x:c>
       <x:c r="C138" s="6" t="str">
-        <x:v>ほうこくする</x:v>
+        <x:v>おくれる</x:v>
       </x:c>
       <x:c r="D138" s="7" t="str">
-        <x:v>报告、汇报</x:v>
+        <x:v>迟到、晚</x:v>
       </x:c>
       <x:c r="E138" s="6" t="str">
         <x:v>[0]</x:v>
       </x:c>
       <x:c r="F138" s="6" t="str">
-        <x:v>三类（サ变）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G138" s="6" t="str">
-        <x:v>報告します</x:v>
+        <x:v>遅れます</x:v>
       </x:c>
       <x:c r="H138" s="6" t="str">
-        <x:v>報告して</x:v>
+        <x:v>遅れて</x:v>
       </x:c>
       <x:c r="I138" s="7" t="str">
-        <x:v>他</x:v>
+        <x:v>自</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="17">
       <x:c r="A139" s="8" t="n">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B139" s="8" t="str">
-        <x:v>見る</x:v>
+        <x:v>報告する</x:v>
       </x:c>
       <x:c r="C139" s="8" t="str">
-        <x:v>みる</x:v>
+        <x:v>ほうこくする</x:v>
       </x:c>
       <x:c r="D139" s="9" t="str">
-        <x:v>看、观看</x:v>
+        <x:v>报告、汇报</x:v>
       </x:c>
       <x:c r="E139" s="8" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F139" s="8" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>三类（サ变）</x:v>
       </x:c>
       <x:c r="G139" s="8" t="str">
-        <x:v>見ます</x:v>
+        <x:v>報告します</x:v>
       </x:c>
       <x:c r="H139" s="8" t="str">
-        <x:v>見て</x:v>
+        <x:v>報告して</x:v>
       </x:c>
       <x:c r="I139" s="9" t="str">
-        <x:v>他；第7课已出现，语法例句复用</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="17">
@@ -6513,28 +6513,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B140" s="6" t="str">
-        <x:v>する</x:v>
+        <x:v>見る</x:v>
       </x:c>
       <x:c r="C140" s="6" t="str">
-        <x:v>する</x:v>
+        <x:v>みる</x:v>
       </x:c>
       <x:c r="D140" s="7" t="str">
-        <x:v>做、干</x:v>
+        <x:v>看、观看</x:v>
       </x:c>
       <x:c r="E140" s="6" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F140" s="6" t="str">
-        <x:v>三类（サ变）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G140" s="6" t="str">
-        <x:v>します</x:v>
+        <x:v>見ます</x:v>
       </x:c>
       <x:c r="H140" s="6" t="str">
-        <x:v>して</x:v>
+        <x:v>見て</x:v>
       </x:c>
       <x:c r="I140" s="7" t="str">
-        <x:v>第7课已出现</x:v>
+        <x:v>他；第7课已出现，语法例句复用</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="17">
@@ -6542,28 +6542,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B141" s="8" t="str">
-        <x:v>言う</x:v>
+        <x:v>する</x:v>
       </x:c>
       <x:c r="C141" s="8" t="str">
-        <x:v>いう</x:v>
+        <x:v>する</x:v>
       </x:c>
       <x:c r="D141" s="9" t="str">
-        <x:v>说、讲</x:v>
+        <x:v>做、干</x:v>
       </x:c>
       <x:c r="E141" s="8" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F141" s="8" t="str">
-        <x:v>一类（五段）</x:v>
+        <x:v>三类（サ变）</x:v>
       </x:c>
       <x:c r="G141" s="8" t="str">
-        <x:v>言います</x:v>
+        <x:v>します</x:v>
       </x:c>
       <x:c r="H141" s="8" t="str">
-        <x:v>言って</x:v>
+        <x:v>して</x:v>
       </x:c>
       <x:c r="I141" s="9" t="str">
-        <x:v>他</x:v>
+        <x:v>第7课已出现</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="17">
@@ -6571,13 +6571,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B142" s="6" t="str">
-        <x:v>帰る</x:v>
+        <x:v>言う</x:v>
       </x:c>
       <x:c r="C142" s="6" t="str">
-        <x:v>かえる</x:v>
+        <x:v>いう</x:v>
       </x:c>
       <x:c r="D142" s="7" t="str">
-        <x:v>回、回去</x:v>
+        <x:v>说、讲</x:v>
       </x:c>
       <x:c r="E142" s="6" t="str">
         <x:v>待核</x:v>
@@ -6586,42 +6586,42 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G142" s="6" t="str">
-        <x:v>帰ります</x:v>
+        <x:v>言います</x:v>
       </x:c>
       <x:c r="H142" s="6" t="str">
-        <x:v>帰って</x:v>
+        <x:v>言って</x:v>
       </x:c>
       <x:c r="I142" s="7" t="str">
-        <x:v>自；第6课已出现</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="17">
       <x:c r="A143" s="8" t="n">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B143" s="8" t="str">
-        <x:v>違う</x:v>
+        <x:v>帰る</x:v>
       </x:c>
       <x:c r="C143" s="8" t="str">
-        <x:v>ちがう</x:v>
+        <x:v>かえる</x:v>
       </x:c>
       <x:c r="D143" s="9" t="str">
-        <x:v>不同、不一样</x:v>
+        <x:v>回、回去</x:v>
       </x:c>
       <x:c r="E143" s="8" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F143" s="8" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G143" s="8" t="str">
-        <x:v>違います</x:v>
+        <x:v>帰ります</x:v>
       </x:c>
       <x:c r="H143" s="8" t="str">
-        <x:v>違って</x:v>
+        <x:v>帰って</x:v>
       </x:c>
       <x:c r="I143" s="9" t="str">
-        <x:v>自</x:v>
+        <x:v>自；第6课已出现</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="17">
@@ -6629,25 +6629,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B144" s="6" t="str">
-        <x:v>混む</x:v>
+        <x:v>違う</x:v>
       </x:c>
       <x:c r="C144" s="6" t="str">
-        <x:v>こむ</x:v>
+        <x:v>ちがう</x:v>
       </x:c>
       <x:c r="D144" s="7" t="str">
-        <x:v>拥挤、混杂</x:v>
+        <x:v>不同、不一样</x:v>
       </x:c>
       <x:c r="E144" s="6" t="str">
-        <x:v>[1]</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F144" s="6" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G144" s="6" t="str">
-        <x:v>混みます</x:v>
+        <x:v>違います</x:v>
       </x:c>
       <x:c r="H144" s="6" t="str">
-        <x:v>混んで</x:v>
+        <x:v>違って</x:v>
       </x:c>
       <x:c r="I144" s="7" t="str">
         <x:v>自</x:v>
@@ -6658,25 +6658,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B145" s="8" t="str">
-        <x:v>決まる</x:v>
+        <x:v>混む</x:v>
       </x:c>
       <x:c r="C145" s="8" t="str">
-        <x:v>きまる</x:v>
+        <x:v>こむ</x:v>
       </x:c>
       <x:c r="D145" s="9" t="str">
-        <x:v>定、决定</x:v>
+        <x:v>拥挤、混杂</x:v>
       </x:c>
       <x:c r="E145" s="8" t="str">
-        <x:v>[0]</x:v>
+        <x:v>[1]</x:v>
       </x:c>
       <x:c r="F145" s="8" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G145" s="8" t="str">
-        <x:v>決まります</x:v>
+        <x:v>混みます</x:v>
       </x:c>
       <x:c r="H145" s="8" t="str">
-        <x:v>決まって</x:v>
+        <x:v>混んで</x:v>
       </x:c>
       <x:c r="I145" s="9" t="str">
         <x:v>自</x:v>
@@ -6687,28 +6687,28 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B146" s="6" t="str">
-        <x:v>確かめる</x:v>
+        <x:v>決まる</x:v>
       </x:c>
       <x:c r="C146" s="6" t="str">
-        <x:v>たしかめる</x:v>
+        <x:v>きまる</x:v>
       </x:c>
       <x:c r="D146" s="7" t="str">
-        <x:v>确认、查明</x:v>
+        <x:v>定、决定</x:v>
       </x:c>
       <x:c r="E146" s="6" t="str">
-        <x:v>[4]</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F146" s="6" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G146" s="6" t="str">
-        <x:v>確かめます</x:v>
+        <x:v>決まります</x:v>
       </x:c>
       <x:c r="H146" s="6" t="str">
-        <x:v>確かめて</x:v>
+        <x:v>決まって</x:v>
       </x:c>
       <x:c r="I146" s="7" t="str">
-        <x:v>他</x:v>
+        <x:v>自</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="17">
@@ -6716,25 +6716,25 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B147" s="8" t="str">
-        <x:v>知らせる</x:v>
+        <x:v>確かめる</x:v>
       </x:c>
       <x:c r="C147" s="8" t="str">
-        <x:v>しらせる</x:v>
+        <x:v>たしかめる</x:v>
       </x:c>
       <x:c r="D147" s="9" t="str">
-        <x:v>告诉、通知</x:v>
+        <x:v>确认、查明</x:v>
       </x:c>
       <x:c r="E147" s="8" t="str">
-        <x:v>[0]</x:v>
+        <x:v>[4]</x:v>
       </x:c>
       <x:c r="F147" s="8" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G147" s="8" t="str">
-        <x:v>知らせます</x:v>
+        <x:v>確かめます</x:v>
       </x:c>
       <x:c r="H147" s="8" t="str">
-        <x:v>知らせて</x:v>
+        <x:v>確かめて</x:v>
       </x:c>
       <x:c r="I147" s="9" t="str">
         <x:v>他</x:v>
@@ -6742,28 +6742,28 @@
     </x:row>
     <x:row r="148" ht="17">
       <x:c r="A148" s="6" t="n">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B148" s="6" t="str">
-        <x:v>思う</x:v>
+        <x:v>知らせる</x:v>
       </x:c>
       <x:c r="C148" s="6" t="str">
-        <x:v>おもう</x:v>
+        <x:v>しらせる</x:v>
       </x:c>
       <x:c r="D148" s="7" t="str">
-        <x:v>想、思考、认为</x:v>
+        <x:v>告诉、通知</x:v>
       </x:c>
       <x:c r="E148" s="6" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F148" s="6" t="str">
-        <x:v>一类（五段）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G148" s="6" t="str">
-        <x:v>思います</x:v>
+        <x:v>知らせます</x:v>
       </x:c>
       <x:c r="H148" s="6" t="str">
-        <x:v>思って</x:v>
+        <x:v>知らせて</x:v>
       </x:c>
       <x:c r="I148" s="7" t="str">
         <x:v>他</x:v>
@@ -6774,13 +6774,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B149" s="8" t="str">
-        <x:v>言う</x:v>
+        <x:v>思う</x:v>
       </x:c>
       <x:c r="C149" s="8" t="str">
-        <x:v>いう</x:v>
+        <x:v>おもう</x:v>
       </x:c>
       <x:c r="D149" s="9" t="str">
-        <x:v>说、讲</x:v>
+        <x:v>想、思考、认为</x:v>
       </x:c>
       <x:c r="E149" s="8" t="str">
         <x:v>待核</x:v>
@@ -6789,13 +6789,13 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G149" s="8" t="str">
-        <x:v>言います</x:v>
+        <x:v>思います</x:v>
       </x:c>
       <x:c r="H149" s="8" t="str">
-        <x:v>言って</x:v>
+        <x:v>思って</x:v>
       </x:c>
       <x:c r="I149" s="9" t="str">
-        <x:v>他；第22课已出现</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="17">
@@ -6803,28 +6803,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B150" s="6" t="str">
-        <x:v>探す</x:v>
+        <x:v>言う</x:v>
       </x:c>
       <x:c r="C150" s="6" t="str">
-        <x:v>さがす</x:v>
+        <x:v>いう</x:v>
       </x:c>
       <x:c r="D150" s="7" t="str">
-        <x:v>找、寻找、寻求</x:v>
+        <x:v>说、讲</x:v>
       </x:c>
       <x:c r="E150" s="6" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F150" s="6" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G150" s="6" t="str">
-        <x:v>探します</x:v>
+        <x:v>言います</x:v>
       </x:c>
       <x:c r="H150" s="6" t="str">
-        <x:v>探して</x:v>
+        <x:v>言って</x:v>
       </x:c>
       <x:c r="I150" s="7" t="str">
-        <x:v>他</x:v>
+        <x:v>他；第22课已出现</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="17">
@@ -6832,13 +6832,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B151" s="8" t="str">
-        <x:v>笑う</x:v>
+        <x:v>探す</x:v>
       </x:c>
       <x:c r="C151" s="8" t="str">
-        <x:v>わらう</x:v>
+        <x:v>さがす</x:v>
       </x:c>
       <x:c r="D151" s="9" t="str">
-        <x:v>笑</x:v>
+        <x:v>找、寻找、寻求</x:v>
       </x:c>
       <x:c r="E151" s="8" t="str">
         <x:v>[0]</x:v>
@@ -6847,13 +6847,13 @@
         <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G151" s="8" t="str">
-        <x:v>笑います</x:v>
+        <x:v>探します</x:v>
       </x:c>
       <x:c r="H151" s="8" t="str">
-        <x:v>笑って</x:v>
+        <x:v>探して</x:v>
       </x:c>
       <x:c r="I151" s="9" t="str">
-        <x:v>自/他视搭配</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="17">
@@ -6861,28 +6861,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B152" s="6" t="str">
-        <x:v>やめる</x:v>
+        <x:v>笑う</x:v>
       </x:c>
       <x:c r="C152" s="6" t="str">
-        <x:v>やめる</x:v>
+        <x:v>わらう</x:v>
       </x:c>
       <x:c r="D152" s="7" t="str">
-        <x:v>戒、停止、放弃；下班</x:v>
+        <x:v>笑</x:v>
       </x:c>
       <x:c r="E152" s="6" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F152" s="6" t="str">
-        <x:v>二类（一段）</x:v>
+        <x:v>一类（五段）</x:v>
       </x:c>
       <x:c r="G152" s="6" t="str">
-        <x:v>やめます</x:v>
+        <x:v>笑います</x:v>
       </x:c>
       <x:c r="H152" s="6" t="str">
-        <x:v>やめて</x:v>
+        <x:v>笑って</x:v>
       </x:c>
       <x:c r="I152" s="7" t="str">
-        <x:v>他/自视搭配</x:v>
+        <x:v>自/他视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -6890,28 +6890,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B153" t="str">
-        <x:v>決める</x:v>
+        <x:v>やめる</x:v>
       </x:c>
       <x:c r="C153" t="str">
-        <x:v>きめる</x:v>
+        <x:v>やめる</x:v>
       </x:c>
       <x:c r="D153" t="str">
-        <x:v>决定</x:v>
+        <x:v>戒、停止、放弃；下班</x:v>
       </x:c>
       <x:c r="E153" t="str">
-        <x:v>[0]</x:v>
+        <x:v>待核</x:v>
       </x:c>
       <x:c r="F153" t="str">
         <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G153" t="str">
-        <x:v>決めます</x:v>
+        <x:v>やめます</x:v>
       </x:c>
       <x:c r="H153" t="str">
-        <x:v>決めて</x:v>
+        <x:v>やめて</x:v>
       </x:c>
       <x:c r="I153" t="str">
-        <x:v>他</x:v>
+        <x:v>他/自视搭配</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -6919,28 +6919,28 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B154" t="str">
-        <x:v>研究する</x:v>
+        <x:v>決める</x:v>
       </x:c>
       <x:c r="C154" t="str">
-        <x:v>けんきゅうする</x:v>
+        <x:v>きめる</x:v>
       </x:c>
       <x:c r="D154" t="str">
-        <x:v>研究</x:v>
+        <x:v>决定</x:v>
       </x:c>
       <x:c r="E154" t="str">
-        <x:v>待核</x:v>
+        <x:v>[0]</x:v>
       </x:c>
       <x:c r="F154" t="str">
-        <x:v>三类（サ变）</x:v>
+        <x:v>二类（一段）</x:v>
       </x:c>
       <x:c r="G154" t="str">
-        <x:v>研究します</x:v>
+        <x:v>決めます</x:v>
       </x:c>
       <x:c r="H154" t="str">
-        <x:v>研究して</x:v>
+        <x:v>決めて</x:v>
       </x:c>
       <x:c r="I154" t="str">
-        <x:v>他/自视搭配</x:v>
+        <x:v>他</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -6948,27 +6948,56 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B155" t="str">
-        <x:v>役に立つ</x:v>
+        <x:v>研究する</x:v>
       </x:c>
       <x:c r="C155" t="str">
-        <x:v>やくにたつ</x:v>
+        <x:v>けんきゅうする</x:v>
       </x:c>
       <x:c r="D155" t="str">
-        <x:v>起作用、有用</x:v>
+        <x:v>研究</x:v>
       </x:c>
       <x:c r="E155" t="str">
         <x:v>待核</x:v>
       </x:c>
       <x:c r="F155" t="str">
+        <x:v>三类（サ变）</x:v>
+      </x:c>
+      <x:c r="G155" t="str">
+        <x:v>研究します</x:v>
+      </x:c>
+      <x:c r="H155" t="str">
+        <x:v>研究して</x:v>
+      </x:c>
+      <x:c r="I155" t="str">
+        <x:v>他/自视搭配</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>役に立つ</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>やくにたつ</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
+        <x:v>起作用、有用</x:v>
+      </x:c>
+      <x:c r="E156" t="str">
+        <x:v>待核</x:v>
+      </x:c>
+      <x:c r="F156" t="str">
         <x:v>一类（五段）</x:v>
       </x:c>
-      <x:c r="G155" t="str">
+      <x:c r="G156" t="str">
         <x:v>役に立ちます</x:v>
       </x:c>
-      <x:c r="H155" t="str">
+      <x:c r="H156" t="str">
         <x:v>役に立って</x:v>
       </x:c>
-      <x:c r="I155" t="str">
+      <x:c r="I156" t="str">
         <x:v>自；词组动词</x:v>
       </x:c>
     </x:row>
@@ -7010,7 +7039,7 @@
         <x:v>518</x:v>
       </x:c>
       <x:c r="B4" s="3" t="n">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="17">
@@ -7018,7 +7047,7 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B5" s="3" t="n">
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34">
@@ -7193,8 +7222,8 @@
       <x:c r="A28">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B28">
-        <x:v>19</x:v>
+      <x:c r="B28" t="n">
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -7243,7 +7272,7 @@
       </x:c>
       <x:c r="B34" s="4" t="n">
         <x:f ca="1">SUM(B13:B33)</x:f>
-        <x:v>154</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/doc/新标日初级上册动词表.xlsx
+++ b/doc/新标日初级上册动词表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动词表" sheetId="1" r:id="R3691361244bf402a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="R9045fe83439247d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="动词表" sheetId="1" r:id="Rd6af89ee4eae41fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="Raaeb85eedf0849e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1617,7 +1617,7 @@
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </x:numFmts>
-  <x:fonts count="25">
+  <x:fonts count="27">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -1752,8 +1752,18 @@
       <x:color theme="1"/>
       <x:name val="宋体"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Source Han Sans SC"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color theme="1"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="35">
+  <x:fills count="37">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1923,6 +1933,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -2169,7 +2189,7 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="28">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
@@ -2194,6 +2214,48 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="35" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="36" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -7001,6 +7063,64 @@
         <x:v>自；词组动词</x:v>
       </x:c>
     </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="16" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B157" s="17" t="str">
+        <x:v>寝坊する</x:v>
+      </x:c>
+      <x:c r="C157" s="17" t="str">
+        <x:v>ねぼうする</x:v>
+      </x:c>
+      <x:c r="D157" s="18" t="str">
+        <x:v>睡懒觉</x:v>
+      </x:c>
+      <x:c r="E157" s="17" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F157" s="17" t="str">
+        <x:v>三类（サ变）</x:v>
+      </x:c>
+      <x:c r="G157" s="17" t="str">
+        <x:v>寝坊します</x:v>
+      </x:c>
+      <x:c r="H157" s="17" t="str">
+        <x:v>寝坊して</x:v>
+      </x:c>
+      <x:c r="I157" s="18" t="str">
+        <x:v>自</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="25" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B158" s="26" t="str">
+        <x:v>外出する</x:v>
+      </x:c>
+      <x:c r="C158" s="26" t="str">
+        <x:v>がいしゅつする</x:v>
+      </x:c>
+      <x:c r="D158" s="27" t="str">
+        <x:v>外出、出去</x:v>
+      </x:c>
+      <x:c r="E158" s="26" t="str">
+        <x:v>[0]</x:v>
+      </x:c>
+      <x:c r="F158" s="26" t="str">
+        <x:v>三类（サ变）</x:v>
+      </x:c>
+      <x:c r="G158" s="26" t="str">
+        <x:v>外出します</x:v>
+      </x:c>
+      <x:c r="H158" s="26" t="str">
+        <x:v>外出して</x:v>
+      </x:c>
+      <x:c r="I158" s="27" t="str">
+        <x:v>自</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -7039,7 +7159,7 @@
         <x:v>518</x:v>
       </x:c>
       <x:c r="B4" s="3" t="n">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="17">
@@ -7047,7 +7167,7 @@
         <x:v>519</x:v>
       </x:c>
       <x:c r="B5" s="3" t="n">
-        <x:v>155</x:v>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34">
@@ -7262,8 +7382,8 @@
       <x:c r="A33">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B33">
-        <x:v>8</x:v>
+      <x:c r="B33" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -7271,8 +7391,8 @@
         <x:v>531</x:v>
       </x:c>
       <x:c r="B34" s="4" t="n">
-        <x:f ca="1">SUM(B13:B33)</x:f>
-        <x:v>155</x:v>
+        <x:f ca="1"/>
+        <x:v>157</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
